--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfanargroup-my.sharepoint.com/personal/ahmed_abdelzaher_alfanar_com/Documents/Desktop/Migration report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2165" documentId="11_FE56DEA76A282FFB01373392047A7FAB0986B2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C93417A3-9C1F-4B23-A3E8-E6078DCA1325}"/>
+  <xr:revisionPtr revIDLastSave="2191" documentId="11_FE56DEA76A282FFB01373392047A7FAB0986B2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03047F1D-3AA2-43B4-87A9-BB933C7A189E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3585" yWindow="3585" windowWidth="21600" windowHeight="12645" tabRatio="744" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3585" yWindow="2835" windowWidth="21600" windowHeight="12645" tabRatio="744" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MADINAH Migration Plan" sheetId="30" state="hidden" r:id="rId1"/>
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="243">
   <si>
     <t>MADINAH Migration Flow</t>
   </si>
@@ -1144,7 +1144,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2640,7 +2640,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="502">
+  <cellXfs count="498">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3791,6 +3791,12 @@
     <xf numFmtId="9" fontId="11" fillId="8" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4010,24 +4016,6 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -4051,10 +4039,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{DD165124-00B3-4A14-921E-82AD1D52CDE4}"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="3" xr:uid="{0D9683E3-9DEF-46D4-8A9E-40FA35F28531}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="27">
     <dxf>
@@ -31820,7 +31808,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:L42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.75" customWidth="1"/>
     <col min="2" max="2" width="5.625" customWidth="1"/>
@@ -31829,9 +31817,9 @@
     <col min="11" max="11" width="42.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="5.45" customHeight="1"/>
-    <row r="2" spans="2:11" ht="24" customHeight="1">
-      <c r="B2" s="436" t="s">
+    <row r="1" spans="2:11" ht="5.45" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="2:11" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B2" s="438" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -31862,56 +31850,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45" customHeight="1">
-      <c r="B3" s="437"/>
-      <c r="C3" s="439" t="s">
+    <row r="3" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="439"/>
+      <c r="C3" s="441" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="440"/>
-      <c r="E3" s="440"/>
-      <c r="F3" s="440"/>
-      <c r="G3" s="440"/>
-      <c r="H3" s="440"/>
-      <c r="I3" s="440"/>
-      <c r="J3" s="440"/>
+      <c r="D3" s="442"/>
+      <c r="E3" s="442"/>
+      <c r="F3" s="442"/>
+      <c r="G3" s="442"/>
+      <c r="H3" s="442"/>
+      <c r="I3" s="442"/>
+      <c r="J3" s="442"/>
       <c r="K3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="45" customHeight="1">
-      <c r="B4" s="437"/>
-      <c r="C4" s="433" t="s">
+    <row r="4" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="439"/>
+      <c r="C4" s="435" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="434"/>
-      <c r="E4" s="434"/>
-      <c r="F4" s="434"/>
-      <c r="G4" s="434"/>
-      <c r="H4" s="434"/>
-      <c r="I4" s="434"/>
-      <c r="J4" s="435"/>
+      <c r="D4" s="436"/>
+      <c r="E4" s="436"/>
+      <c r="F4" s="436"/>
+      <c r="G4" s="436"/>
+      <c r="H4" s="436"/>
+      <c r="I4" s="436"/>
+      <c r="J4" s="437"/>
       <c r="K4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="45" customHeight="1">
-      <c r="B5" s="437"/>
-      <c r="C5" s="433" t="s">
+    <row r="5" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="439"/>
+      <c r="C5" s="435" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="434"/>
-      <c r="E5" s="434"/>
-      <c r="F5" s="434"/>
-      <c r="G5" s="434"/>
-      <c r="H5" s="434"/>
-      <c r="I5" s="434"/>
-      <c r="J5" s="435"/>
+      <c r="D5" s="436"/>
+      <c r="E5" s="436"/>
+      <c r="F5" s="436"/>
+      <c r="G5" s="436"/>
+      <c r="H5" s="436"/>
+      <c r="I5" s="436"/>
+      <c r="J5" s="437"/>
       <c r="K5" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="45" customHeight="1">
-      <c r="B6" s="437"/>
+    <row r="6" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="439"/>
       <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
@@ -31926,168 +31914,168 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="45" customHeight="1">
-      <c r="B7" s="437"/>
-      <c r="C7" s="433" t="s">
+    <row r="7" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="439"/>
+      <c r="C7" s="435" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="434"/>
-      <c r="E7" s="434"/>
-      <c r="F7" s="434"/>
-      <c r="G7" s="434"/>
-      <c r="H7" s="434"/>
-      <c r="I7" s="434"/>
-      <c r="J7" s="435"/>
+      <c r="D7" s="436"/>
+      <c r="E7" s="436"/>
+      <c r="F7" s="436"/>
+      <c r="G7" s="436"/>
+      <c r="H7" s="436"/>
+      <c r="I7" s="436"/>
+      <c r="J7" s="437"/>
       <c r="K7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="45" customHeight="1">
-      <c r="B8" s="437"/>
-      <c r="C8" s="433" t="s">
+    <row r="8" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="439"/>
+      <c r="C8" s="435" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="434"/>
-      <c r="E8" s="434"/>
-      <c r="F8" s="434"/>
-      <c r="G8" s="434"/>
-      <c r="H8" s="434"/>
-      <c r="I8" s="434"/>
-      <c r="J8" s="435"/>
+      <c r="D8" s="436"/>
+      <c r="E8" s="436"/>
+      <c r="F8" s="436"/>
+      <c r="G8" s="436"/>
+      <c r="H8" s="436"/>
+      <c r="I8" s="436"/>
+      <c r="J8" s="437"/>
       <c r="K8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="45" customHeight="1">
-      <c r="B9" s="437"/>
-      <c r="C9" s="433" t="s">
+    <row r="9" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="439"/>
+      <c r="C9" s="435" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="434"/>
-      <c r="E9" s="434"/>
-      <c r="F9" s="434"/>
-      <c r="G9" s="434"/>
-      <c r="H9" s="434"/>
-      <c r="I9" s="434"/>
-      <c r="J9" s="435"/>
+      <c r="D9" s="436"/>
+      <c r="E9" s="436"/>
+      <c r="F9" s="436"/>
+      <c r="G9" s="436"/>
+      <c r="H9" s="436"/>
+      <c r="I9" s="436"/>
+      <c r="J9" s="437"/>
       <c r="K9" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="45" customHeight="1">
-      <c r="B10" s="437"/>
-      <c r="C10" s="433" t="s">
+    <row r="10" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="439"/>
+      <c r="C10" s="435" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="434"/>
-      <c r="E10" s="434"/>
-      <c r="F10" s="434"/>
-      <c r="G10" s="434"/>
-      <c r="H10" s="434"/>
-      <c r="I10" s="434"/>
-      <c r="J10" s="435"/>
+      <c r="D10" s="436"/>
+      <c r="E10" s="436"/>
+      <c r="F10" s="436"/>
+      <c r="G10" s="436"/>
+      <c r="H10" s="436"/>
+      <c r="I10" s="436"/>
+      <c r="J10" s="437"/>
       <c r="K10" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="45" customHeight="1">
-      <c r="B11" s="437"/>
-      <c r="C11" s="433" t="s">
+    <row r="11" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="439"/>
+      <c r="C11" s="435" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="434"/>
-      <c r="E11" s="434"/>
-      <c r="F11" s="434"/>
-      <c r="G11" s="434"/>
-      <c r="H11" s="434"/>
-      <c r="I11" s="434"/>
-      <c r="J11" s="435"/>
+      <c r="D11" s="436"/>
+      <c r="E11" s="436"/>
+      <c r="F11" s="436"/>
+      <c r="G11" s="436"/>
+      <c r="H11" s="436"/>
+      <c r="I11" s="436"/>
+      <c r="J11" s="437"/>
       <c r="K11" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="45" customHeight="1">
-      <c r="B12" s="437"/>
-      <c r="C12" s="433" t="s">
+    <row r="12" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="439"/>
+      <c r="C12" s="435" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="434"/>
-      <c r="E12" s="434"/>
-      <c r="F12" s="434"/>
-      <c r="G12" s="434"/>
-      <c r="H12" s="434"/>
-      <c r="I12" s="434"/>
-      <c r="J12" s="435"/>
+      <c r="D12" s="436"/>
+      <c r="E12" s="436"/>
+      <c r="F12" s="436"/>
+      <c r="G12" s="436"/>
+      <c r="H12" s="436"/>
+      <c r="I12" s="436"/>
+      <c r="J12" s="437"/>
       <c r="K12" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="45" customHeight="1">
-      <c r="B13" s="437"/>
-      <c r="C13" s="433" t="s">
+    <row r="13" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="439"/>
+      <c r="C13" s="435" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="434"/>
-      <c r="E13" s="434"/>
-      <c r="F13" s="434"/>
-      <c r="G13" s="434"/>
-      <c r="H13" s="434"/>
-      <c r="I13" s="434"/>
-      <c r="J13" s="435"/>
+      <c r="D13" s="436"/>
+      <c r="E13" s="436"/>
+      <c r="F13" s="436"/>
+      <c r="G13" s="436"/>
+      <c r="H13" s="436"/>
+      <c r="I13" s="436"/>
+      <c r="J13" s="437"/>
       <c r="K13" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="45" customHeight="1">
-      <c r="B14" s="437"/>
-      <c r="C14" s="433" t="s">
+    <row r="14" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="439"/>
+      <c r="C14" s="435" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="434"/>
-      <c r="E14" s="434"/>
-      <c r="F14" s="434"/>
-      <c r="G14" s="434"/>
-      <c r="H14" s="434"/>
-      <c r="I14" s="434"/>
-      <c r="J14" s="435"/>
+      <c r="D14" s="436"/>
+      <c r="E14" s="436"/>
+      <c r="F14" s="436"/>
+      <c r="G14" s="436"/>
+      <c r="H14" s="436"/>
+      <c r="I14" s="436"/>
+      <c r="J14" s="437"/>
       <c r="K14" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="45" customHeight="1">
-      <c r="B15" s="437"/>
-      <c r="C15" s="433" t="s">
+    <row r="15" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="439"/>
+      <c r="C15" s="435" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="434"/>
-      <c r="E15" s="434"/>
-      <c r="F15" s="434"/>
-      <c r="G15" s="434"/>
-      <c r="H15" s="434"/>
-      <c r="I15" s="434"/>
-      <c r="J15" s="435"/>
+      <c r="D15" s="436"/>
+      <c r="E15" s="436"/>
+      <c r="F15" s="436"/>
+      <c r="G15" s="436"/>
+      <c r="H15" s="436"/>
+      <c r="I15" s="436"/>
+      <c r="J15" s="437"/>
       <c r="K15" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="45" customHeight="1">
-      <c r="B16" s="437"/>
-      <c r="C16" s="433" t="s">
+    <row r="16" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="439"/>
+      <c r="C16" s="435" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="434"/>
-      <c r="E16" s="434"/>
-      <c r="F16" s="434"/>
-      <c r="G16" s="434"/>
-      <c r="H16" s="434"/>
-      <c r="I16" s="434"/>
-      <c r="J16" s="435"/>
+      <c r="D16" s="436"/>
+      <c r="E16" s="436"/>
+      <c r="F16" s="436"/>
+      <c r="G16" s="436"/>
+      <c r="H16" s="436"/>
+      <c r="I16" s="436"/>
+      <c r="J16" s="437"/>
       <c r="K16" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="45" customHeight="1">
-      <c r="B17" s="437"/>
+    <row r="17" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="439"/>
       <c r="C17" s="7" t="s">
         <v>27</v>
       </c>
@@ -32102,76 +32090,76 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="45" customHeight="1">
-      <c r="B18" s="437"/>
-      <c r="C18" s="439" t="s">
+    <row r="18" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="439"/>
+      <c r="C18" s="441" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="439"/>
-      <c r="E18" s="439"/>
-      <c r="F18" s="439"/>
-      <c r="G18" s="439"/>
-      <c r="H18" s="439"/>
-      <c r="I18" s="439"/>
-      <c r="J18" s="439"/>
+      <c r="D18" s="441"/>
+      <c r="E18" s="441"/>
+      <c r="F18" s="441"/>
+      <c r="G18" s="441"/>
+      <c r="H18" s="441"/>
+      <c r="I18" s="441"/>
+      <c r="J18" s="441"/>
       <c r="K18" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="2:12" ht="43.5" customHeight="1">
-      <c r="B19" s="437"/>
-      <c r="C19" s="439" t="s">
+    <row r="19" spans="2:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="439"/>
+      <c r="C19" s="441" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="439"/>
-      <c r="E19" s="439"/>
-      <c r="F19" s="439"/>
-      <c r="G19" s="439"/>
-      <c r="H19" s="439"/>
-      <c r="I19" s="439"/>
-      <c r="J19" s="439"/>
+      <c r="D19" s="441"/>
+      <c r="E19" s="441"/>
+      <c r="F19" s="441"/>
+      <c r="G19" s="441"/>
+      <c r="H19" s="441"/>
+      <c r="I19" s="441"/>
+      <c r="J19" s="441"/>
       <c r="K19" s="6" t="s">
         <v>30</v>
       </c>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="2:12" ht="36" customHeight="1">
-      <c r="B20" s="437"/>
-      <c r="C20" s="433" t="s">
+    <row r="20" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="439"/>
+      <c r="C20" s="435" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="434"/>
-      <c r="E20" s="434"/>
-      <c r="F20" s="434"/>
-      <c r="G20" s="434"/>
-      <c r="H20" s="434"/>
-      <c r="I20" s="434"/>
-      <c r="J20" s="435"/>
+      <c r="D20" s="436"/>
+      <c r="E20" s="436"/>
+      <c r="F20" s="436"/>
+      <c r="G20" s="436"/>
+      <c r="H20" s="436"/>
+      <c r="I20" s="436"/>
+      <c r="J20" s="437"/>
       <c r="K20" s="6" t="s">
         <v>33</v>
       </c>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="2:12" ht="36" customHeight="1">
-      <c r="B21" s="437"/>
-      <c r="C21" s="433" t="s">
+    <row r="21" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="439"/>
+      <c r="C21" s="435" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="434"/>
-      <c r="E21" s="434"/>
-      <c r="F21" s="434"/>
-      <c r="G21" s="434"/>
-      <c r="H21" s="434"/>
-      <c r="I21" s="434"/>
-      <c r="J21" s="435"/>
+      <c r="D21" s="436"/>
+      <c r="E21" s="436"/>
+      <c r="F21" s="436"/>
+      <c r="G21" s="436"/>
+      <c r="H21" s="436"/>
+      <c r="I21" s="436"/>
+      <c r="J21" s="437"/>
       <c r="K21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B22" s="437"/>
+    <row r="22" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="439"/>
       <c r="C22" s="7" t="s">
         <v>36</v>
       </c>
@@ -32187,8 +32175,8 @@
       </c>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B23" s="437"/>
+    <row r="23" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="439"/>
       <c r="C23" s="7" t="s">
         <v>38</v>
       </c>
@@ -32204,8 +32192,8 @@
       </c>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B24" s="437"/>
+    <row r="24" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="439"/>
       <c r="C24" s="7" t="s">
         <v>40</v>
       </c>
@@ -32221,8 +32209,8 @@
       </c>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B25" s="437"/>
+    <row r="25" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="439"/>
       <c r="C25" s="7" t="s">
         <v>41</v>
       </c>
@@ -32238,8 +32226,8 @@
       </c>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B26" s="437"/>
+    <row r="26" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="439"/>
       <c r="C26" s="7" t="s">
         <v>43</v>
       </c>
@@ -32255,8 +32243,8 @@
       </c>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B27" s="437"/>
+    <row r="27" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="439"/>
       <c r="C27" s="7" t="s">
         <v>44</v>
       </c>
@@ -32272,8 +32260,8 @@
       </c>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B28" s="437"/>
+    <row r="28" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="439"/>
       <c r="C28" s="7" t="s">
         <v>46</v>
       </c>
@@ -32289,8 +32277,8 @@
       </c>
       <c r="L28" s="1"/>
     </row>
-    <row r="29" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B29" s="437"/>
+    <row r="29" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="439"/>
       <c r="C29" s="11" t="s">
         <v>47</v>
       </c>
@@ -32304,8 +32292,8 @@
       <c r="K29" s="6"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" spans="2:12" ht="28.9" customHeight="1">
-      <c r="B30" s="437"/>
+    <row r="30" spans="2:12" ht="28.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="439"/>
       <c r="C30" s="11" t="s">
         <v>48</v>
       </c>
@@ -32319,39 +32307,39 @@
       <c r="K30" s="6"/>
       <c r="L30" s="1"/>
     </row>
-    <row r="31" spans="2:12" ht="36" customHeight="1">
-      <c r="B31" s="437"/>
-      <c r="C31" s="433" t="s">
+    <row r="31" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="439"/>
+      <c r="C31" s="435" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="434"/>
-      <c r="E31" s="434"/>
-      <c r="F31" s="434"/>
-      <c r="G31" s="434"/>
-      <c r="H31" s="434"/>
-      <c r="I31" s="434"/>
-      <c r="J31" s="435"/>
+      <c r="D31" s="436"/>
+      <c r="E31" s="436"/>
+      <c r="F31" s="436"/>
+      <c r="G31" s="436"/>
+      <c r="H31" s="436"/>
+      <c r="I31" s="436"/>
+      <c r="J31" s="437"/>
       <c r="K31" s="6" t="s">
         <v>50</v>
       </c>
       <c r="L31" s="1"/>
     </row>
-    <row r="32" spans="2:12" ht="36" customHeight="1">
-      <c r="B32" s="438"/>
-      <c r="C32" s="433" t="s">
+    <row r="32" spans="2:12" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="440"/>
+      <c r="C32" s="435" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="434"/>
-      <c r="E32" s="434"/>
-      <c r="F32" s="434"/>
-      <c r="G32" s="434"/>
-      <c r="H32" s="434"/>
-      <c r="I32" s="434"/>
-      <c r="J32" s="435"/>
+      <c r="D32" s="436"/>
+      <c r="E32" s="436"/>
+      <c r="F32" s="436"/>
+      <c r="G32" s="436"/>
+      <c r="H32" s="436"/>
+      <c r="I32" s="436"/>
+      <c r="J32" s="437"/>
       <c r="K32" s="6"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="4:11">
+    <row r="33" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -32361,7 +32349,7 @@
       <c r="J33" s="1"/>
       <c r="K33" s="12"/>
     </row>
-    <row r="34" spans="4:11">
+    <row r="34" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -32371,7 +32359,7 @@
       <c r="J34" s="1"/>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="4:11">
+    <row r="35" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -32380,7 +32368,7 @@
       <c r="J35" s="1"/>
       <c r="K35" s="12"/>
     </row>
-    <row r="36" spans="4:11">
+    <row r="36" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -32390,7 +32378,7 @@
       <c r="J36" s="1"/>
       <c r="K36" s="12"/>
     </row>
-    <row r="37" spans="4:11">
+    <row r="37" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -32400,7 +32388,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="12"/>
     </row>
-    <row r="38" spans="4:11">
+    <row r="38" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -32410,7 +32398,7 @@
       <c r="J38" s="1"/>
       <c r="K38" s="12"/>
     </row>
-    <row r="39" spans="4:11">
+    <row r="39" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -32420,7 +32408,7 @@
       <c r="J39" s="1"/>
       <c r="K39" s="12"/>
     </row>
-    <row r="42" spans="4:11">
+    <row r="42" spans="4:11" x14ac:dyDescent="0.15">
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
@@ -32432,7 +32420,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C5:J5"/>
     <mergeCell ref="C7:J7"/>
     <mergeCell ref="C8:J8"/>
     <mergeCell ref="C20:J20"/>
@@ -32452,6 +32439,7 @@
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C3:J3"/>
     <mergeCell ref="C4:J4"/>
+    <mergeCell ref="C5:J5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -32465,7 +32453,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.875" style="376" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="376" hidden="1" customWidth="1"/>
@@ -32488,7 +32476,7 @@
     <col min="28" max="16384" width="9" style="376"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.6" customHeight="1">
+    <row r="1" spans="1:26" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="373">
         <v>0</v>
       </c>
@@ -32498,30 +32486,30 @@
       <c r="C1" s="375" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="445" t="s">
+      <c r="D1" s="447" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="446"/>
-      <c r="F1" s="446"/>
-      <c r="G1" s="446"/>
-      <c r="H1" s="446"/>
-      <c r="I1" s="446"/>
-      <c r="J1" s="446"/>
-      <c r="K1" s="446"/>
-      <c r="L1" s="446"/>
-      <c r="M1" s="446"/>
-      <c r="N1" s="446"/>
-      <c r="O1" s="446"/>
-      <c r="P1" s="446"/>
-      <c r="Q1" s="446"/>
-      <c r="R1" s="446"/>
-      <c r="S1" s="446"/>
-      <c r="T1" s="446"/>
-      <c r="U1" s="446"/>
-      <c r="V1" s="446"/>
-      <c r="W1" s="446"/>
+      <c r="E1" s="448"/>
+      <c r="F1" s="448"/>
+      <c r="G1" s="448"/>
+      <c r="H1" s="448"/>
+      <c r="I1" s="448"/>
+      <c r="J1" s="448"/>
+      <c r="K1" s="448"/>
+      <c r="L1" s="448"/>
+      <c r="M1" s="448"/>
+      <c r="N1" s="448"/>
+      <c r="O1" s="448"/>
+      <c r="P1" s="448"/>
+      <c r="Q1" s="448"/>
+      <c r="R1" s="448"/>
+      <c r="S1" s="448"/>
+      <c r="T1" s="448"/>
+      <c r="U1" s="448"/>
+      <c r="V1" s="448"/>
+      <c r="W1" s="448"/>
     </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
+    <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="373">
         <v>0.5</v>
       </c>
@@ -32531,28 +32519,28 @@
       <c r="C2" s="375" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="447"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
-      <c r="J2" s="448"/>
-      <c r="K2" s="448"/>
-      <c r="L2" s="448"/>
-      <c r="M2" s="448"/>
-      <c r="N2" s="448"/>
-      <c r="O2" s="448"/>
-      <c r="P2" s="448"/>
-      <c r="Q2" s="448"/>
-      <c r="R2" s="448"/>
-      <c r="S2" s="448"/>
-      <c r="T2" s="448"/>
-      <c r="U2" s="448"/>
-      <c r="V2" s="448"/>
-      <c r="W2" s="448"/>
+      <c r="D2" s="449"/>
+      <c r="E2" s="450"/>
+      <c r="F2" s="450"/>
+      <c r="G2" s="450"/>
+      <c r="H2" s="450"/>
+      <c r="I2" s="450"/>
+      <c r="J2" s="450"/>
+      <c r="K2" s="450"/>
+      <c r="L2" s="450"/>
+      <c r="M2" s="450"/>
+      <c r="N2" s="450"/>
+      <c r="O2" s="450"/>
+      <c r="P2" s="450"/>
+      <c r="Q2" s="450"/>
+      <c r="R2" s="450"/>
+      <c r="S2" s="450"/>
+      <c r="T2" s="450"/>
+      <c r="U2" s="450"/>
+      <c r="V2" s="450"/>
+      <c r="W2" s="450"/>
     </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
+    <row r="3" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="373">
         <v>1</v>
       </c>
@@ -32562,84 +32550,84 @@
       <c r="C3" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="447"/>
-      <c r="E3" s="448"/>
-      <c r="F3" s="448"/>
-      <c r="G3" s="448"/>
-      <c r="H3" s="448"/>
-      <c r="I3" s="448"/>
-      <c r="J3" s="448"/>
-      <c r="K3" s="448"/>
-      <c r="L3" s="448"/>
-      <c r="M3" s="448"/>
-      <c r="N3" s="448"/>
-      <c r="O3" s="448"/>
-      <c r="P3" s="448"/>
-      <c r="Q3" s="448"/>
-      <c r="R3" s="448"/>
-      <c r="S3" s="448"/>
-      <c r="T3" s="448"/>
-      <c r="U3" s="448"/>
-      <c r="V3" s="448"/>
-      <c r="W3" s="448"/>
+      <c r="D3" s="449"/>
+      <c r="E3" s="450"/>
+      <c r="F3" s="450"/>
+      <c r="G3" s="450"/>
+      <c r="H3" s="450"/>
+      <c r="I3" s="450"/>
+      <c r="J3" s="450"/>
+      <c r="K3" s="450"/>
+      <c r="L3" s="450"/>
+      <c r="M3" s="450"/>
+      <c r="N3" s="450"/>
+      <c r="O3" s="450"/>
+      <c r="P3" s="450"/>
+      <c r="Q3" s="450"/>
+      <c r="R3" s="450"/>
+      <c r="S3" s="450"/>
+      <c r="T3" s="450"/>
+      <c r="U3" s="450"/>
+      <c r="V3" s="450"/>
+      <c r="W3" s="450"/>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="377"/>
       <c r="B4" s="378"/>
       <c r="C4" s="379"/>
-      <c r="D4" s="449"/>
-      <c r="E4" s="449"/>
-      <c r="F4" s="449"/>
-      <c r="G4" s="449"/>
-      <c r="H4" s="449"/>
-      <c r="I4" s="449"/>
-      <c r="J4" s="449"/>
-      <c r="K4" s="449"/>
-      <c r="L4" s="449"/>
-      <c r="M4" s="449"/>
-      <c r="N4" s="449"/>
-      <c r="O4" s="449"/>
-      <c r="P4" s="449"/>
-      <c r="Q4" s="449"/>
-      <c r="R4" s="449"/>
-      <c r="S4" s="449"/>
-      <c r="T4" s="449"/>
-      <c r="U4" s="449"/>
-      <c r="V4" s="449"/>
-      <c r="W4" s="449"/>
+      <c r="D4" s="451"/>
+      <c r="E4" s="451"/>
+      <c r="F4" s="451"/>
+      <c r="G4" s="451"/>
+      <c r="H4" s="451"/>
+      <c r="I4" s="451"/>
+      <c r="J4" s="451"/>
+      <c r="K4" s="451"/>
+      <c r="L4" s="451"/>
+      <c r="M4" s="451"/>
+      <c r="N4" s="451"/>
+      <c r="O4" s="451"/>
+      <c r="P4" s="451"/>
+      <c r="Q4" s="451"/>
+      <c r="R4" s="451"/>
+      <c r="S4" s="451"/>
+      <c r="T4" s="451"/>
+      <c r="U4" s="451"/>
+      <c r="V4" s="451"/>
+      <c r="W4" s="451"/>
     </row>
-    <row r="5" spans="1:26" ht="35.1" customHeight="1">
-      <c r="A5" s="444" t="s">
+    <row r="5" spans="1:26" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="446" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="444"/>
-      <c r="C5" s="444"/>
-      <c r="D5" s="444"/>
-      <c r="E5" s="444"/>
-      <c r="F5" s="444"/>
-      <c r="G5" s="444"/>
-      <c r="H5" s="450"/>
-      <c r="I5" s="444" t="s">
+      <c r="B5" s="446"/>
+      <c r="C5" s="446"/>
+      <c r="D5" s="446"/>
+      <c r="E5" s="446"/>
+      <c r="F5" s="446"/>
+      <c r="G5" s="446"/>
+      <c r="H5" s="452"/>
+      <c r="I5" s="446" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="444"/>
-      <c r="K5" s="444"/>
-      <c r="L5" s="444"/>
-      <c r="M5" s="444"/>
-      <c r="N5" s="444"/>
-      <c r="O5" s="444"/>
-      <c r="P5" s="450"/>
-      <c r="Q5" s="444" t="s">
+      <c r="J5" s="446"/>
+      <c r="K5" s="446"/>
+      <c r="L5" s="446"/>
+      <c r="M5" s="446"/>
+      <c r="N5" s="446"/>
+      <c r="O5" s="446"/>
+      <c r="P5" s="452"/>
+      <c r="Q5" s="446" t="s">
         <v>58</v>
       </c>
-      <c r="R5" s="444"/>
-      <c r="S5" s="444"/>
-      <c r="T5" s="444"/>
-      <c r="U5" s="444"/>
-      <c r="V5" s="444"/>
-      <c r="W5" s="444"/>
+      <c r="R5" s="446"/>
+      <c r="S5" s="446"/>
+      <c r="T5" s="446"/>
+      <c r="U5" s="446"/>
+      <c r="V5" s="446"/>
+      <c r="W5" s="446"/>
     </row>
-    <row r="6" spans="1:26" s="384" customFormat="1" ht="88.5">
+    <row r="6" spans="1:26" s="384" customFormat="1" ht="88.5" x14ac:dyDescent="0.15">
       <c r="A6" s="380" t="s">
         <v>59</v>
       </c>
@@ -32661,7 +32649,7 @@
       <c r="G6" s="383" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="451"/>
+      <c r="H6" s="453"/>
       <c r="I6" s="380" t="s">
         <v>59</v>
       </c>
@@ -32683,7 +32671,7 @@
       <c r="O6" s="383" t="s">
         <v>65</v>
       </c>
-      <c r="P6" s="451"/>
+      <c r="P6" s="453"/>
       <c r="Q6" s="380" t="s">
         <v>59</v>
       </c>
@@ -32709,7 +32697,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="385" t="s">
         <v>68</v>
       </c>
@@ -32737,7 +32725,7 @@
         <f t="array" ref="G7">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A7)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="451"/>
+      <c r="H7" s="453"/>
       <c r="I7" s="385" t="s">
         <v>68</v>
       </c>
@@ -32765,7 +32753,7 @@
         <f t="array" ref="O7">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A7)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="451"/>
+      <c r="P7" s="453"/>
       <c r="Q7" s="385" t="s">
         <v>68</v>
       </c>
@@ -32794,7 +32782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="8" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="385" t="s">
         <v>69</v>
       </c>
@@ -32822,7 +32810,7 @@
         <f t="array" ref="G8">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A8)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="451"/>
+      <c r="H8" s="453"/>
       <c r="I8" s="385" t="s">
         <v>69</v>
       </c>
@@ -32850,7 +32838,7 @@
         <f t="array" ref="O8">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A8)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="451"/>
+      <c r="P8" s="453"/>
       <c r="Q8" s="385" t="s">
         <v>69</v>
       </c>
@@ -32879,7 +32867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="9" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="385" t="s">
         <v>70</v>
       </c>
@@ -32907,7 +32895,7 @@
         <f t="array" ref="G9">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A9)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H9" s="451"/>
+      <c r="H9" s="453"/>
       <c r="I9" s="385" t="s">
         <v>70</v>
       </c>
@@ -32935,7 +32923,7 @@
         <f t="array" ref="O9">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A9)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="451"/>
+      <c r="P9" s="453"/>
       <c r="Q9" s="385" t="s">
         <v>70</v>
       </c>
@@ -32964,7 +32952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="385" t="s">
         <v>71</v>
       </c>
@@ -32992,7 +32980,7 @@
         <f t="array" ref="G10">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A10)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H10" s="451"/>
+      <c r="H10" s="453"/>
       <c r="I10" s="385" t="s">
         <v>71</v>
       </c>
@@ -33020,7 +33008,7 @@
         <f t="array" ref="O10">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A10)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P10" s="451"/>
+      <c r="P10" s="453"/>
       <c r="Q10" s="385" t="s">
         <v>71</v>
       </c>
@@ -33049,7 +33037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="385" t="s">
         <v>72</v>
       </c>
@@ -33077,7 +33065,7 @@
         <f t="array" ref="G11">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A11)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="451"/>
+      <c r="H11" s="453"/>
       <c r="I11" s="385" t="s">
         <v>72</v>
       </c>
@@ -33105,7 +33093,7 @@
         <f t="array" ref="O11">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A11)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P11" s="451"/>
+      <c r="P11" s="453"/>
       <c r="Q11" s="385" t="s">
         <v>72</v>
       </c>
@@ -33134,7 +33122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="12" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="385" t="s">
         <v>73</v>
       </c>
@@ -33162,7 +33150,7 @@
         <f t="array" ref="G12">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A12)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H12" s="451"/>
+      <c r="H12" s="453"/>
       <c r="I12" s="385" t="s">
         <v>73</v>
       </c>
@@ -33190,7 +33178,7 @@
         <f t="array" ref="O12">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A12)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P12" s="451"/>
+      <c r="P12" s="453"/>
       <c r="Q12" s="385" t="s">
         <v>73</v>
       </c>
@@ -33219,7 +33207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="13" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="385" t="s">
         <v>74</v>
       </c>
@@ -33247,7 +33235,7 @@
         <f t="array" ref="G13">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A13)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="451"/>
+      <c r="H13" s="453"/>
       <c r="I13" s="385" t="s">
         <v>74</v>
       </c>
@@ -33275,7 +33263,7 @@
         <f t="array" ref="O13">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A13)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P13" s="451"/>
+      <c r="P13" s="453"/>
       <c r="Q13" s="385" t="s">
         <v>74</v>
       </c>
@@ -33304,7 +33292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="14" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="385" t="s">
         <v>75</v>
       </c>
@@ -33332,7 +33320,7 @@
         <f t="array" ref="G14">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A14)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H14" s="451"/>
+      <c r="H14" s="453"/>
       <c r="I14" s="385" t="s">
         <v>75</v>
       </c>
@@ -33360,7 +33348,7 @@
         <f t="array" ref="O14">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A14)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="451"/>
+      <c r="P14" s="453"/>
       <c r="Q14" s="385" t="s">
         <v>75</v>
       </c>
@@ -33389,7 +33377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="15" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="385" t="s">
         <v>76</v>
       </c>
@@ -33417,7 +33405,7 @@
         <f t="array" ref="G15">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A15)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="451"/>
+      <c r="H15" s="453"/>
       <c r="I15" s="385" t="s">
         <v>76</v>
       </c>
@@ -33445,7 +33433,7 @@
         <f t="array" ref="O15">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A15)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P15" s="451"/>
+      <c r="P15" s="453"/>
       <c r="Q15" s="385" t="s">
         <v>76</v>
       </c>
@@ -33474,7 +33462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="16" spans="1:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="385" t="s">
         <v>77</v>
       </c>
@@ -33502,7 +33490,7 @@
         <f t="array" ref="G16">IFERROR(INDEX('MADINAH Migration Plan-'!$L:$L,MATCH(1,('MADINAH Migration Plan-'!$AA:$AA=$A16)*('MADINAH Migration Plan-'!$Z:$Z=G$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="452"/>
+      <c r="H16" s="454"/>
       <c r="I16" s="385" t="s">
         <v>77</v>
       </c>
@@ -33530,7 +33518,7 @@
         <f t="array" ref="O16">IFERROR(INDEX('Jeddah Migration Plan'!$L:$L,MATCH(1,('Jeddah Migration Plan'!$AB:$AB=$A16)*('Jeddah Migration Plan'!$AA:$AA=O$6),0)),0)</f>
         <v>0</v>
       </c>
-      <c r="P16" s="452"/>
+      <c r="P16" s="454"/>
       <c r="Q16" s="385" t="s">
         <v>77</v>
       </c>
@@ -33559,61 +33547,61 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="441"/>
-      <c r="B17" s="442"/>
-      <c r="C17" s="442"/>
-      <c r="D17" s="442"/>
-      <c r="E17" s="442"/>
-      <c r="F17" s="442"/>
-      <c r="G17" s="442"/>
-      <c r="H17" s="443"/>
-      <c r="I17" s="443"/>
-      <c r="J17" s="443"/>
-      <c r="K17" s="443"/>
-      <c r="L17" s="443"/>
-      <c r="M17" s="443"/>
-      <c r="N17" s="443"/>
-      <c r="O17" s="443"/>
-      <c r="P17" s="443"/>
-      <c r="Q17" s="443"/>
-      <c r="R17" s="443"/>
-      <c r="S17" s="443"/>
-      <c r="T17" s="443"/>
-      <c r="U17" s="443"/>
-      <c r="V17" s="443"/>
-      <c r="W17" s="443"/>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A17" s="443"/>
+      <c r="B17" s="444"/>
+      <c r="C17" s="444"/>
+      <c r="D17" s="444"/>
+      <c r="E17" s="444"/>
+      <c r="F17" s="444"/>
+      <c r="G17" s="444"/>
+      <c r="H17" s="445"/>
+      <c r="I17" s="445"/>
+      <c r="J17" s="445"/>
+      <c r="K17" s="445"/>
+      <c r="L17" s="445"/>
+      <c r="M17" s="445"/>
+      <c r="N17" s="445"/>
+      <c r="O17" s="445"/>
+      <c r="P17" s="445"/>
+      <c r="Q17" s="445"/>
+      <c r="R17" s="445"/>
+      <c r="S17" s="445"/>
+      <c r="T17" s="445"/>
+      <c r="U17" s="445"/>
+      <c r="V17" s="445"/>
+      <c r="W17" s="445"/>
     </row>
-    <row r="18" spans="1:23" ht="35.1" customHeight="1">
-      <c r="A18" s="444" t="s">
+    <row r="18" spans="1:23" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="446" t="s">
         <v>78</v>
       </c>
-      <c r="B18" s="444"/>
-      <c r="C18" s="444"/>
-      <c r="D18" s="444"/>
-      <c r="E18" s="444"/>
-      <c r="F18" s="444"/>
-      <c r="G18" s="444"/>
+      <c r="B18" s="446"/>
+      <c r="C18" s="446"/>
+      <c r="D18" s="446"/>
+      <c r="E18" s="446"/>
+      <c r="F18" s="446"/>
+      <c r="G18" s="446"/>
       <c r="H18" s="390"/>
-      <c r="I18" s="453"/>
-      <c r="J18" s="453"/>
-      <c r="K18" s="453"/>
-      <c r="L18" s="453"/>
-      <c r="M18" s="453"/>
-      <c r="N18" s="453"/>
-      <c r="O18" s="453"/>
+      <c r="I18" s="455"/>
+      <c r="J18" s="455"/>
+      <c r="K18" s="455"/>
+      <c r="L18" s="455"/>
+      <c r="M18" s="455"/>
+      <c r="N18" s="455"/>
+      <c r="O18" s="455"/>
       <c r="P18" s="391"/>
-      <c r="Q18" s="444" t="s">
+      <c r="Q18" s="446" t="s">
         <v>79</v>
       </c>
-      <c r="R18" s="444"/>
-      <c r="S18" s="444"/>
-      <c r="T18" s="444"/>
-      <c r="U18" s="444"/>
-      <c r="V18" s="444"/>
-      <c r="W18" s="444"/>
+      <c r="R18" s="446"/>
+      <c r="S18" s="446"/>
+      <c r="T18" s="446"/>
+      <c r="U18" s="446"/>
+      <c r="V18" s="446"/>
+      <c r="W18" s="446"/>
     </row>
-    <row r="19" spans="1:23" ht="86.25" customHeight="1">
+    <row r="19" spans="1:23" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="380" t="s">
         <v>59</v>
       </c>
@@ -33636,13 +33624,13 @@
         <v>65</v>
       </c>
       <c r="H19" s="392"/>
-      <c r="I19" s="454"/>
-      <c r="J19" s="454"/>
-      <c r="K19" s="454"/>
-      <c r="L19" s="454"/>
-      <c r="M19" s="454"/>
-      <c r="N19" s="454"/>
-      <c r="O19" s="454"/>
+      <c r="I19" s="456"/>
+      <c r="J19" s="456"/>
+      <c r="K19" s="456"/>
+      <c r="L19" s="456"/>
+      <c r="M19" s="456"/>
+      <c r="N19" s="456"/>
+      <c r="O19" s="456"/>
       <c r="P19" s="393"/>
       <c r="Q19" s="380" t="s">
         <v>59</v>
@@ -33666,7 +33654,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="385" t="s">
         <v>68</v>
       </c>
@@ -33695,13 +33683,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="392"/>
-      <c r="I20" s="454"/>
-      <c r="J20" s="454"/>
-      <c r="K20" s="454"/>
-      <c r="L20" s="454"/>
-      <c r="M20" s="454"/>
-      <c r="N20" s="454"/>
-      <c r="O20" s="454"/>
+      <c r="I20" s="456"/>
+      <c r="J20" s="456"/>
+      <c r="K20" s="456"/>
+      <c r="L20" s="456"/>
+      <c r="M20" s="456"/>
+      <c r="N20" s="456"/>
+      <c r="O20" s="456"/>
       <c r="P20" s="393"/>
       <c r="Q20" s="385" t="s">
         <v>68</v>
@@ -33731,7 +33719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="385" t="s">
         <v>69</v>
       </c>
@@ -33760,13 +33748,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="392"/>
-      <c r="I21" s="454"/>
-      <c r="J21" s="454"/>
-      <c r="K21" s="454"/>
-      <c r="L21" s="454"/>
-      <c r="M21" s="454"/>
-      <c r="N21" s="454"/>
-      <c r="O21" s="454"/>
+      <c r="I21" s="456"/>
+      <c r="J21" s="456"/>
+      <c r="K21" s="456"/>
+      <c r="L21" s="456"/>
+      <c r="M21" s="456"/>
+      <c r="N21" s="456"/>
+      <c r="O21" s="456"/>
       <c r="P21" s="393"/>
       <c r="Q21" s="385" t="s">
         <v>69</v>
@@ -33796,7 +33784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="385" t="s">
         <v>70</v>
       </c>
@@ -33825,13 +33813,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="392"/>
-      <c r="I22" s="454"/>
-      <c r="J22" s="454"/>
-      <c r="K22" s="454"/>
-      <c r="L22" s="454"/>
-      <c r="M22" s="454"/>
-      <c r="N22" s="454"/>
-      <c r="O22" s="454"/>
+      <c r="I22" s="456"/>
+      <c r="J22" s="456"/>
+      <c r="K22" s="456"/>
+      <c r="L22" s="456"/>
+      <c r="M22" s="456"/>
+      <c r="N22" s="456"/>
+      <c r="O22" s="456"/>
       <c r="P22" s="393"/>
       <c r="Q22" s="385" t="s">
         <v>70</v>
@@ -33861,7 +33849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="385" t="s">
         <v>71</v>
       </c>
@@ -33890,13 +33878,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="392"/>
-      <c r="I23" s="454"/>
-      <c r="J23" s="454"/>
-      <c r="K23" s="454"/>
-      <c r="L23" s="454"/>
-      <c r="M23" s="454"/>
-      <c r="N23" s="454"/>
-      <c r="O23" s="454"/>
+      <c r="I23" s="456"/>
+      <c r="J23" s="456"/>
+      <c r="K23" s="456"/>
+      <c r="L23" s="456"/>
+      <c r="M23" s="456"/>
+      <c r="N23" s="456"/>
+      <c r="O23" s="456"/>
       <c r="P23" s="393"/>
       <c r="Q23" s="385" t="s">
         <v>71</v>
@@ -33926,7 +33914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="385" t="s">
         <v>72</v>
       </c>
@@ -33955,13 +33943,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="392"/>
-      <c r="I24" s="454"/>
-      <c r="J24" s="454"/>
-      <c r="K24" s="454"/>
-      <c r="L24" s="454"/>
-      <c r="M24" s="454"/>
-      <c r="N24" s="454"/>
-      <c r="O24" s="454"/>
+      <c r="I24" s="456"/>
+      <c r="J24" s="456"/>
+      <c r="K24" s="456"/>
+      <c r="L24" s="456"/>
+      <c r="M24" s="456"/>
+      <c r="N24" s="456"/>
+      <c r="O24" s="456"/>
       <c r="P24" s="393"/>
       <c r="Q24" s="385" t="s">
         <v>72</v>
@@ -33991,7 +33979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="385" t="s">
         <v>73</v>
       </c>
@@ -34020,13 +34008,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="392"/>
-      <c r="I25" s="454"/>
-      <c r="J25" s="454"/>
-      <c r="K25" s="454"/>
-      <c r="L25" s="454"/>
-      <c r="M25" s="454"/>
-      <c r="N25" s="454"/>
-      <c r="O25" s="454"/>
+      <c r="I25" s="456"/>
+      <c r="J25" s="456"/>
+      <c r="K25" s="456"/>
+      <c r="L25" s="456"/>
+      <c r="M25" s="456"/>
+      <c r="N25" s="456"/>
+      <c r="O25" s="456"/>
       <c r="P25" s="393"/>
       <c r="Q25" s="385" t="s">
         <v>73</v>
@@ -34056,7 +34044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="385" t="s">
         <v>74</v>
       </c>
@@ -34085,13 +34073,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="392"/>
-      <c r="I26" s="454"/>
-      <c r="J26" s="454"/>
-      <c r="K26" s="454"/>
-      <c r="L26" s="454"/>
-      <c r="M26" s="454"/>
-      <c r="N26" s="454"/>
-      <c r="O26" s="454"/>
+      <c r="I26" s="456"/>
+      <c r="J26" s="456"/>
+      <c r="K26" s="456"/>
+      <c r="L26" s="456"/>
+      <c r="M26" s="456"/>
+      <c r="N26" s="456"/>
+      <c r="O26" s="456"/>
       <c r="P26" s="393"/>
       <c r="Q26" s="385" t="s">
         <v>74</v>
@@ -34121,7 +34109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1">
+    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="385" t="s">
         <v>75</v>
       </c>
@@ -34150,13 +34138,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="394"/>
-      <c r="I27" s="455"/>
-      <c r="J27" s="455"/>
-      <c r="K27" s="455"/>
-      <c r="L27" s="455"/>
-      <c r="M27" s="455"/>
-      <c r="N27" s="455"/>
-      <c r="O27" s="455"/>
+      <c r="I27" s="457"/>
+      <c r="J27" s="457"/>
+      <c r="K27" s="457"/>
+      <c r="L27" s="457"/>
+      <c r="M27" s="457"/>
+      <c r="N27" s="457"/>
+      <c r="O27" s="457"/>
       <c r="P27" s="395"/>
       <c r="Q27" s="385" t="s">
         <v>75</v>
@@ -34374,6 +34362,25 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="11" id="{79F30A10-B97F-44AE-911C-6718F507306B}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>A1:A3</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{0B1936DE-2B3A-41B4-8605-894F823D7635}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" direction="leftToRight">
               <x14:cfvo type="formula">
@@ -34464,6 +34471,44 @@
           <xm:sqref>C20:C27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="28" id="{2495DCDF-3D3F-4A02-8806-9F561637C177}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D7:G16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="29" id="{0CEA0DD7-BC64-42B6-9DED-4A410C9D9ACA}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>D20:G27</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{F4AE4576-6169-44FE-BE90-0F2C4B64D504}">
             <x14:dataBar minLength="0" maxLength="100" gradient="0" direction="rightToLeft">
               <x14:cfvo type="formula">
@@ -34492,6 +34537,25 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>K7:K16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="4" id="{AC8C5D6B-7351-409C-899F-424C1C4C4F11}">
+            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
+              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
+              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L7:O16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{E3EAA460-85B0-440E-AF62-C1FF33FB6A5C}">
@@ -34554,82 +34618,6 @@
           <xm:sqref>S20:S27</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{79F30A10-B97F-44AE-911C-6718F507306B}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>A1:A3</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="28" id="{2495DCDF-3D3F-4A02-8806-9F561637C177}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D7:G16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="29" id="{0CEA0DD7-BC64-42B6-9DED-4A410C9D9ACA}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>D20:G27</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{AC8C5D6B-7351-409C-899F-424C1C4C4F11}">
-            <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num" gte="0">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:cfIcon iconSet="3Symbols" iconId="0"/>
-              <x14:cfIcon iconSet="4Arrows" iconId="2"/>
-              <x14:cfIcon iconSet="3Symbols" iconId="2"/>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L7:O16</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="3" id="{BF362FC8-1C73-4C6F-AEE5-FBDDE90680F0}">
             <x14:iconSet iconSet="3Symbols" showValue="0" custom="1">
               <x14:cfvo type="percent">
@@ -34676,7 +34664,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B4BB28-03E4-4B08-BA95-267094CE3CB6}">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.5" bestFit="1" customWidth="1"/>
@@ -34693,25 +34681,25 @@
     <col min="13" max="13" width="12.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="98" customFormat="1" ht="18.75">
-      <c r="A1" s="419" t="s">
+    <row r="1" spans="1:14" s="98" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="421" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="420"/>
-      <c r="C1" s="420"/>
-      <c r="D1" s="420"/>
-      <c r="E1" s="420"/>
-      <c r="F1" s="421"/>
-      <c r="H1" s="419" t="s">
+      <c r="B1" s="422"/>
+      <c r="C1" s="422"/>
+      <c r="D1" s="422"/>
+      <c r="E1" s="422"/>
+      <c r="F1" s="423"/>
+      <c r="H1" s="421" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="420"/>
-      <c r="J1" s="420"/>
-      <c r="K1" s="420"/>
-      <c r="L1" s="420"/>
-      <c r="M1" s="421"/>
+      <c r="I1" s="422"/>
+      <c r="J1" s="422"/>
+      <c r="K1" s="422"/>
+      <c r="L1" s="422"/>
+      <c r="M1" s="423"/>
     </row>
-    <row r="2" spans="1:14" s="99" customFormat="1" ht="24.75" customHeight="1">
+    <row r="2" spans="1:14" s="99" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="408"/>
       <c r="B2" s="409"/>
       <c r="C2" s="397" t="s">
@@ -34741,8 +34729,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75">
-      <c r="A3" s="422" t="s">
+    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="424" t="s">
         <v>86</v>
       </c>
       <c r="B3" s="399" t="s">
@@ -34764,7 +34752,7 @@
         <f>E3-D3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="422" t="s">
+      <c r="H3" s="424" t="s">
         <v>86</v>
       </c>
       <c r="I3" s="399" t="s">
@@ -34788,8 +34776,8 @@
       </c>
       <c r="N3" s="396"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75">
-      <c r="A4" s="422"/>
+    <row r="4" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="424"/>
       <c r="B4" s="399" t="s">
         <v>88</v>
       </c>
@@ -34809,7 +34797,7 @@
         <f>E4-D4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="422"/>
+      <c r="H4" s="424"/>
       <c r="I4" s="399" t="s">
         <v>88</v>
       </c>
@@ -34830,8 +34818,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.75">
-      <c r="A5" s="422"/>
+    <row r="5" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="424"/>
       <c r="B5" s="399" t="s">
         <v>89</v>
       </c>
@@ -34851,7 +34839,7 @@
         <f t="shared" ref="F5:F11" si="0">E5-D5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="422"/>
+      <c r="H5" s="424"/>
       <c r="I5" s="399" t="s">
         <v>89</v>
       </c>
@@ -34872,8 +34860,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15.75">
-      <c r="A6" s="422"/>
+    <row r="6" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="424"/>
       <c r="B6" s="399" t="s">
         <v>90</v>
       </c>
@@ -34893,7 +34881,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="422"/>
+      <c r="H6" s="424"/>
       <c r="I6" s="399" t="s">
         <v>90</v>
       </c>
@@ -34914,22 +34902,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="9" customHeight="1">
-      <c r="A7" s="416"/>
-      <c r="B7" s="417"/>
-      <c r="C7" s="417"/>
-      <c r="D7" s="417"/>
-      <c r="E7" s="417"/>
-      <c r="F7" s="418"/>
-      <c r="H7" s="416"/>
-      <c r="I7" s="417"/>
-      <c r="J7" s="417"/>
-      <c r="K7" s="417"/>
-      <c r="L7" s="417"/>
-      <c r="M7" s="418"/>
+    <row r="7" spans="1:14" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="418"/>
+      <c r="B7" s="419"/>
+      <c r="C7" s="419"/>
+      <c r="D7" s="419"/>
+      <c r="E7" s="419"/>
+      <c r="F7" s="420"/>
+      <c r="H7" s="418"/>
+      <c r="I7" s="419"/>
+      <c r="J7" s="419"/>
+      <c r="K7" s="419"/>
+      <c r="L7" s="419"/>
+      <c r="M7" s="420"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75">
-      <c r="A8" s="422" t="s">
+    <row r="8" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="424" t="s">
         <v>91</v>
       </c>
       <c r="B8" s="399" t="s">
@@ -34951,7 +34939,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="422" t="s">
+      <c r="H8" s="424" t="s">
         <v>91</v>
       </c>
       <c r="I8" s="399" t="s">
@@ -34974,8 +34962,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75">
-      <c r="A9" s="422"/>
+    <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="424"/>
       <c r="B9" s="399" t="s">
         <v>88</v>
       </c>
@@ -34995,7 +34983,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="422"/>
+      <c r="H9" s="424"/>
       <c r="I9" s="399" t="s">
         <v>88</v>
       </c>
@@ -35016,8 +35004,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75">
-      <c r="A10" s="422"/>
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="424"/>
       <c r="B10" s="399" t="s">
         <v>89</v>
       </c>
@@ -35037,7 +35025,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="422"/>
+      <c r="H10" s="424"/>
       <c r="I10" s="399" t="s">
         <v>89</v>
       </c>
@@ -35058,8 +35046,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A11" s="423"/>
+    <row r="11" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="425"/>
       <c r="B11" s="399" t="s">
         <v>90</v>
       </c>
@@ -35079,7 +35067,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="423"/>
+      <c r="H11" s="425"/>
       <c r="I11" s="399" t="s">
         <v>90</v>
       </c>
@@ -35100,26 +35088,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14.25" thickBot="1"/>
-    <row r="13" spans="1:14" ht="18.75">
-      <c r="A13" s="419" t="s">
+    <row r="12" spans="1:14" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="421" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="420"/>
-      <c r="C13" s="420"/>
-      <c r="D13" s="420"/>
-      <c r="E13" s="420"/>
-      <c r="F13" s="421"/>
-      <c r="H13" s="419" t="s">
+      <c r="B13" s="422"/>
+      <c r="C13" s="422"/>
+      <c r="D13" s="422"/>
+      <c r="E13" s="422"/>
+      <c r="F13" s="423"/>
+      <c r="H13" s="421" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="420"/>
-      <c r="J13" s="420"/>
-      <c r="K13" s="420"/>
-      <c r="L13" s="420"/>
-      <c r="M13" s="421"/>
+      <c r="I13" s="422"/>
+      <c r="J13" s="422"/>
+      <c r="K13" s="422"/>
+      <c r="L13" s="422"/>
+      <c r="M13" s="423"/>
     </row>
-    <row r="14" spans="1:14" ht="15.75">
+    <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="408"/>
       <c r="B14" s="409"/>
       <c r="C14" s="397" t="s">
@@ -35149,8 +35137,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15.75">
-      <c r="A15" s="422" t="s">
+    <row r="15" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="424" t="s">
         <v>86</v>
       </c>
       <c r="B15" s="399" t="s">
@@ -35161,18 +35149,18 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="D15" s="410">
-        <f>'Jeddah Migration Plan'!G53</f>
-        <v>46335</v>
+        <f>'Jeddah Migration Plan'!G54</f>
+        <v>46338</v>
       </c>
       <c r="E15" s="403">
-        <f>'Jeddah Migration Plan'!I53</f>
-        <v>46335</v>
+        <f>'Jeddah Migration Plan'!I54</f>
+        <v>46338</v>
       </c>
       <c r="F15" s="404">
         <f>E15-D15</f>
         <v>0</v>
       </c>
-      <c r="H15" s="422" t="s">
+      <c r="H15" s="424" t="s">
         <v>86</v>
       </c>
       <c r="I15" s="399" t="s">
@@ -35195,8 +35183,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15.75">
-      <c r="A16" s="422"/>
+    <row r="16" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="424"/>
       <c r="B16" s="399" t="s">
         <v>88</v>
       </c>
@@ -35216,7 +35204,7 @@
         <f>E16-D16</f>
         <v>0</v>
       </c>
-      <c r="H16" s="422"/>
+      <c r="H16" s="424"/>
       <c r="I16" s="399" t="s">
         <v>88</v>
       </c>
@@ -35237,8 +35225,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="15.75">
-      <c r="A17" s="422"/>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="424"/>
       <c r="B17" s="399" t="s">
         <v>89</v>
       </c>
@@ -35258,7 +35246,7 @@
         <f t="shared" ref="F17:F18" si="3">E17-D17</f>
         <v>0</v>
       </c>
-      <c r="H17" s="422"/>
+      <c r="H17" s="424"/>
       <c r="I17" s="399" t="s">
         <v>89</v>
       </c>
@@ -35279,8 +35267,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="15.75">
-      <c r="A18" s="422"/>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="424"/>
       <c r="B18" s="399" t="s">
         <v>90</v>
       </c>
@@ -35300,7 +35288,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H18" s="422"/>
+      <c r="H18" s="424"/>
       <c r="I18" s="399" t="s">
         <v>90</v>
       </c>
@@ -35321,22 +35309,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="416"/>
-      <c r="B19" s="417"/>
-      <c r="C19" s="417"/>
-      <c r="D19" s="417"/>
-      <c r="E19" s="417"/>
-      <c r="F19" s="418"/>
-      <c r="H19" s="416"/>
-      <c r="I19" s="417"/>
-      <c r="J19" s="417"/>
-      <c r="K19" s="417"/>
-      <c r="L19" s="417"/>
-      <c r="M19" s="418"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A19" s="418"/>
+      <c r="B19" s="419"/>
+      <c r="C19" s="419"/>
+      <c r="D19" s="419"/>
+      <c r="E19" s="419"/>
+      <c r="F19" s="420"/>
+      <c r="H19" s="418"/>
+      <c r="I19" s="419"/>
+      <c r="J19" s="419"/>
+      <c r="K19" s="419"/>
+      <c r="L19" s="419"/>
+      <c r="M19" s="420"/>
     </row>
-    <row r="20" spans="1:13" ht="15.75">
-      <c r="A20" s="422" t="s">
+    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="424" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="399" t="s">
@@ -35358,7 +35346,7 @@
         <f t="shared" ref="F20:F23" si="5">E20-D20</f>
         <v>0</v>
       </c>
-      <c r="H20" s="422" t="s">
+      <c r="H20" s="424" t="s">
         <v>91</v>
       </c>
       <c r="I20" s="399" t="s">
@@ -35381,8 +35369,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="15.75">
-      <c r="A21" s="422"/>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="424"/>
       <c r="B21" s="399" t="s">
         <v>88</v>
       </c>
@@ -35402,7 +35390,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H21" s="422"/>
+      <c r="H21" s="424"/>
       <c r="I21" s="399" t="s">
         <v>88</v>
       </c>
@@ -35423,8 +35411,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="15.75">
-      <c r="A22" s="422"/>
+    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="424"/>
       <c r="B22" s="399" t="s">
         <v>89</v>
       </c>
@@ -35444,7 +35432,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H22" s="422"/>
+      <c r="H22" s="424"/>
       <c r="I22" s="399" t="s">
         <v>89</v>
       </c>
@@ -35465,8 +35453,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" thickBot="1">
-      <c r="A23" s="423"/>
+    <row r="23" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="425"/>
       <c r="B23" s="399" t="s">
         <v>90</v>
       </c>
@@ -35486,7 +35474,7 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H23" s="423"/>
+      <c r="H23" s="425"/>
       <c r="I23" s="399" t="s">
         <v>90</v>
       </c>
@@ -35507,24 +35495,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="14.25" thickBot="1"/>
-    <row r="25" spans="1:13" ht="18.75">
-      <c r="A25" s="419" t="s">
+    <row r="24" spans="1:13" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="421" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="420"/>
-      <c r="C25" s="420"/>
-      <c r="D25" s="420"/>
-      <c r="E25" s="420"/>
-      <c r="F25" s="421"/>
-      <c r="H25" s="424"/>
-      <c r="I25" s="425"/>
-      <c r="J25" s="425"/>
-      <c r="K25" s="425"/>
-      <c r="L25" s="425"/>
-      <c r="M25" s="426"/>
+      <c r="B25" s="422"/>
+      <c r="C25" s="422"/>
+      <c r="D25" s="422"/>
+      <c r="E25" s="422"/>
+      <c r="F25" s="423"/>
+      <c r="H25" s="426"/>
+      <c r="I25" s="427"/>
+      <c r="J25" s="427"/>
+      <c r="K25" s="427"/>
+      <c r="L25" s="427"/>
+      <c r="M25" s="428"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="408"/>
       <c r="B26" s="409"/>
       <c r="C26" s="397" t="s">
@@ -35539,15 +35527,15 @@
       <c r="F26" s="398" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="427"/>
-      <c r="I26" s="428"/>
-      <c r="J26" s="428"/>
-      <c r="K26" s="428"/>
-      <c r="L26" s="428"/>
-      <c r="M26" s="429"/>
+      <c r="H26" s="429"/>
+      <c r="I26" s="430"/>
+      <c r="J26" s="430"/>
+      <c r="K26" s="430"/>
+      <c r="L26" s="430"/>
+      <c r="M26" s="431"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A27" s="422" t="s">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="424" t="s">
         <v>86</v>
       </c>
       <c r="B27" s="399" t="s">
@@ -35569,15 +35557,15 @@
         <f>E27-D27</f>
         <v>0</v>
       </c>
-      <c r="H27" s="427"/>
-      <c r="I27" s="428"/>
-      <c r="J27" s="428"/>
-      <c r="K27" s="428"/>
-      <c r="L27" s="428"/>
-      <c r="M27" s="429"/>
+      <c r="H27" s="429"/>
+      <c r="I27" s="430"/>
+      <c r="J27" s="430"/>
+      <c r="K27" s="430"/>
+      <c r="L27" s="430"/>
+      <c r="M27" s="431"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A28" s="422"/>
+    <row r="28" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="424"/>
       <c r="B28" s="399" t="s">
         <v>88</v>
       </c>
@@ -35597,15 +35585,15 @@
         <f>E28-D28</f>
         <v>0</v>
       </c>
-      <c r="H28" s="427"/>
-      <c r="I28" s="428"/>
-      <c r="J28" s="428"/>
-      <c r="K28" s="428"/>
-      <c r="L28" s="428"/>
-      <c r="M28" s="429"/>
+      <c r="H28" s="429"/>
+      <c r="I28" s="430"/>
+      <c r="J28" s="430"/>
+      <c r="K28" s="430"/>
+      <c r="L28" s="430"/>
+      <c r="M28" s="431"/>
     </row>
-    <row r="29" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A29" s="422"/>
+    <row r="29" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="424"/>
       <c r="B29" s="399" t="s">
         <v>89</v>
       </c>
@@ -35625,15 +35613,15 @@
         <f t="shared" ref="F29:F30" si="7">E29-D29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="427"/>
-      <c r="I29" s="428"/>
-      <c r="J29" s="428"/>
-      <c r="K29" s="428"/>
-      <c r="L29" s="428"/>
-      <c r="M29" s="429"/>
+      <c r="H29" s="429"/>
+      <c r="I29" s="430"/>
+      <c r="J29" s="430"/>
+      <c r="K29" s="430"/>
+      <c r="L29" s="430"/>
+      <c r="M29" s="431"/>
     </row>
-    <row r="30" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A30" s="422"/>
+    <row r="30" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="424"/>
       <c r="B30" s="399" t="s">
         <v>90</v>
       </c>
@@ -35653,29 +35641,29 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H30" s="427"/>
-      <c r="I30" s="428"/>
-      <c r="J30" s="428"/>
-      <c r="K30" s="428"/>
-      <c r="L30" s="428"/>
-      <c r="M30" s="429"/>
+      <c r="H30" s="429"/>
+      <c r="I30" s="430"/>
+      <c r="J30" s="430"/>
+      <c r="K30" s="430"/>
+      <c r="L30" s="430"/>
+      <c r="M30" s="431"/>
     </row>
-    <row r="31" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A31" s="416"/>
-      <c r="B31" s="417"/>
-      <c r="C31" s="417"/>
-      <c r="D31" s="417"/>
-      <c r="E31" s="417"/>
-      <c r="F31" s="418"/>
-      <c r="H31" s="427"/>
-      <c r="I31" s="428"/>
-      <c r="J31" s="428"/>
-      <c r="K31" s="428"/>
-      <c r="L31" s="428"/>
-      <c r="M31" s="429"/>
+    <row r="31" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="418"/>
+      <c r="B31" s="419"/>
+      <c r="C31" s="419"/>
+      <c r="D31" s="419"/>
+      <c r="E31" s="419"/>
+      <c r="F31" s="420"/>
+      <c r="H31" s="429"/>
+      <c r="I31" s="430"/>
+      <c r="J31" s="430"/>
+      <c r="K31" s="430"/>
+      <c r="L31" s="430"/>
+      <c r="M31" s="431"/>
     </row>
-    <row r="32" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A32" s="422" t="s">
+    <row r="32" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="424" t="s">
         <v>91</v>
       </c>
       <c r="B32" s="399" t="s">
@@ -35697,15 +35685,15 @@
         <f t="shared" ref="F32:F35" si="8">E32-D32</f>
         <v>0</v>
       </c>
-      <c r="H32" s="427"/>
-      <c r="I32" s="428"/>
-      <c r="J32" s="428"/>
-      <c r="K32" s="428"/>
-      <c r="L32" s="428"/>
-      <c r="M32" s="429"/>
+      <c r="H32" s="429"/>
+      <c r="I32" s="430"/>
+      <c r="J32" s="430"/>
+      <c r="K32" s="430"/>
+      <c r="L32" s="430"/>
+      <c r="M32" s="431"/>
     </row>
-    <row r="33" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A33" s="422"/>
+    <row r="33" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="424"/>
       <c r="B33" s="399" t="s">
         <v>88</v>
       </c>
@@ -35725,15 +35713,15 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H33" s="427"/>
-      <c r="I33" s="428"/>
-      <c r="J33" s="428"/>
-      <c r="K33" s="428"/>
-      <c r="L33" s="428"/>
-      <c r="M33" s="429"/>
+      <c r="H33" s="429"/>
+      <c r="I33" s="430"/>
+      <c r="J33" s="430"/>
+      <c r="K33" s="430"/>
+      <c r="L33" s="430"/>
+      <c r="M33" s="431"/>
     </row>
-    <row r="34" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A34" s="422"/>
+    <row r="34" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="424"/>
       <c r="B34" s="399" t="s">
         <v>89</v>
       </c>
@@ -35753,15 +35741,15 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H34" s="427"/>
-      <c r="I34" s="428"/>
-      <c r="J34" s="428"/>
-      <c r="K34" s="428"/>
-      <c r="L34" s="428"/>
-      <c r="M34" s="429"/>
+      <c r="H34" s="429"/>
+      <c r="I34" s="430"/>
+      <c r="J34" s="430"/>
+      <c r="K34" s="430"/>
+      <c r="L34" s="430"/>
+      <c r="M34" s="431"/>
     </row>
-    <row r="35" spans="1:13" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A35" s="423"/>
+    <row r="35" spans="1:13" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="425"/>
       <c r="B35" s="400" t="s">
         <v>95</v>
       </c>
@@ -35781,12 +35769,12 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H35" s="430"/>
-      <c r="I35" s="431"/>
-      <c r="J35" s="431"/>
-      <c r="K35" s="431"/>
-      <c r="L35" s="431"/>
-      <c r="M35" s="432"/>
+      <c r="H35" s="432"/>
+      <c r="I35" s="433"/>
+      <c r="J35" s="433"/>
+      <c r="K35" s="433"/>
+      <c r="L35" s="433"/>
+      <c r="M35" s="434"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -35825,11 +35813,11 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AE76"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.75" style="230" customWidth="1"/>
-    <col min="2" max="2" width="9" style="230" customWidth="1"/>
-    <col min="3" max="3" width="16" style="230" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="230" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.25" style="230" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.75" style="230" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="229" customWidth="1"/>
     <col min="6" max="6" width="16.75" style="233" customWidth="1"/>
@@ -35854,7 +35842,7 @@
     <col min="32" max="16384" width="9" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="5.45" customHeight="1">
+    <row r="1" spans="2:31" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="257"/>
       <c r="G1" s="257"/>
       <c r="H1" s="257"/>
@@ -35868,7 +35856,7 @@
       <c r="N1" s="258"/>
       <c r="O1" s="259"/>
     </row>
-    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1">
+    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="261"/>
       <c r="C2" s="261" t="s">
         <v>96</v>
@@ -35932,7 +35920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="3" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="270"/>
       <c r="C3" s="270"/>
       <c r="D3" s="270"/>
@@ -35960,8 +35948,8 @@
       <c r="AA3" s="275"/>
       <c r="AB3" s="275"/>
     </row>
-    <row r="4" spans="2:31" ht="45" customHeight="1">
-      <c r="B4" s="456" t="s">
+    <row r="4" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="458" t="s">
         <v>104</v>
       </c>
       <c r="C4" s="248" t="s">
@@ -36018,8 +36006,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="5" spans="2:31" ht="45" customHeight="1">
-      <c r="B5" s="457"/>
+    <row r="5" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="459"/>
       <c r="C5" s="249" t="s">
         <v>86</v>
       </c>
@@ -36078,8 +36066,8 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="6" spans="2:31" ht="88.5" customHeight="1">
-      <c r="B6" s="457"/>
+    <row r="6" spans="2:31" ht="88.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="459"/>
       <c r="C6" s="249" t="s">
         <v>86</v>
       </c>
@@ -36125,8 +36113,8 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="7" spans="2:31" ht="45" customHeight="1">
-      <c r="B7" s="457"/>
+    <row r="7" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="459"/>
       <c r="C7" s="249" t="s">
         <v>86</v>
       </c>
@@ -36187,8 +36175,8 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="8" spans="2:31" ht="45" customHeight="1">
-      <c r="B8" s="458"/>
+    <row r="8" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="460"/>
       <c r="C8" s="252" t="s">
         <v>86</v>
       </c>
@@ -36249,7 +36237,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="9" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="9" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="281"/>
       <c r="C9" s="281"/>
       <c r="D9" s="281"/>
@@ -36278,8 +36266,8 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="10" spans="2:31" ht="45" customHeight="1">
-      <c r="B10" s="459" t="s">
+    <row r="10" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="461" t="s">
         <v>116</v>
       </c>
       <c r="C10" s="285" t="s">
@@ -36333,8 +36321,8 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="11" spans="2:31" ht="45" customHeight="1">
-      <c r="B11" s="460"/>
+    <row r="11" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="462"/>
       <c r="C11" s="285" t="s">
         <v>86</v>
       </c>
@@ -36385,8 +36373,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="2:31" ht="45" customHeight="1">
-      <c r="B12" s="460"/>
+    <row r="12" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="462"/>
       <c r="C12" s="285" t="s">
         <v>86</v>
       </c>
@@ -36441,8 +36429,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="2:31" ht="45" customHeight="1">
-      <c r="B13" s="460"/>
+    <row r="13" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="462"/>
       <c r="C13" s="285" t="s">
         <v>86</v>
       </c>
@@ -36497,7 +36485,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="14" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="292"/>
       <c r="C14" s="292"/>
       <c r="D14" s="292"/>
@@ -36523,8 +36511,8 @@
       <c r="Z14" s="275"/>
       <c r="AA14" s="275"/>
     </row>
-    <row r="15" spans="2:31" ht="45" customHeight="1">
-      <c r="B15" s="461" t="s">
+    <row r="15" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="463" t="s">
         <v>118</v>
       </c>
       <c r="C15" s="296" t="s">
@@ -36579,8 +36567,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="2:31" ht="45" customHeight="1">
-      <c r="B16" s="462"/>
+    <row r="16" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="464"/>
       <c r="C16" s="296" t="s">
         <v>86</v>
       </c>
@@ -36633,8 +36621,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="2:31" ht="45" customHeight="1">
-      <c r="B17" s="462"/>
+    <row r="17" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="464"/>
       <c r="C17" s="296" t="s">
         <v>86</v>
       </c>
@@ -36689,8 +36677,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:31" ht="45" customHeight="1">
-      <c r="B18" s="462"/>
+    <row r="18" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="464"/>
       <c r="C18" s="296" t="s">
         <v>86</v>
       </c>
@@ -36745,7 +36733,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="19" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="292"/>
       <c r="C19" s="292"/>
       <c r="D19" s="292"/>
@@ -36771,8 +36759,8 @@
       <c r="Z19" s="275"/>
       <c r="AA19" s="275"/>
     </row>
-    <row r="20" spans="2:31" ht="45" customHeight="1">
-      <c r="B20" s="459" t="s">
+    <row r="20" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="461" t="s">
         <v>119</v>
       </c>
       <c r="C20" s="285" t="s">
@@ -36828,8 +36816,8 @@
       </c>
       <c r="AE20" s="276"/>
     </row>
-    <row r="21" spans="2:31" ht="45" customHeight="1">
-      <c r="B21" s="460"/>
+    <row r="21" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="462"/>
       <c r="C21" s="285" t="s">
         <v>86</v>
       </c>
@@ -36884,8 +36872,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="2:31" ht="45" customHeight="1">
-      <c r="B22" s="460"/>
+    <row r="22" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="462"/>
       <c r="C22" s="285" t="s">
         <v>86</v>
       </c>
@@ -36940,8 +36928,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:31" ht="45" customHeight="1">
-      <c r="B23" s="460"/>
+    <row r="23" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="462"/>
       <c r="C23" s="285" t="s">
         <v>86</v>
       </c>
@@ -36996,7 +36984,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="24" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="292"/>
       <c r="C24" s="292"/>
       <c r="D24" s="292"/>
@@ -37024,8 +37012,8 @@
       <c r="Z24" s="275"/>
       <c r="AA24" s="275"/>
     </row>
-    <row r="25" spans="2:31" ht="45" customHeight="1">
-      <c r="B25" s="461" t="s">
+    <row r="25" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="463" t="s">
         <v>121</v>
       </c>
       <c r="C25" s="296" t="s">
@@ -37080,8 +37068,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="2:31" ht="45" customHeight="1">
-      <c r="B26" s="462"/>
+    <row r="26" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="464"/>
       <c r="C26" s="296" t="s">
         <v>86</v>
       </c>
@@ -37134,8 +37122,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="2:31" ht="45" customHeight="1">
-      <c r="B27" s="462"/>
+    <row r="27" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="464"/>
       <c r="C27" s="296" t="s">
         <v>86</v>
       </c>
@@ -37190,8 +37178,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:31" ht="45" customHeight="1">
-      <c r="B28" s="462"/>
+    <row r="28" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="464"/>
       <c r="C28" s="296" t="s">
         <v>86</v>
       </c>
@@ -37246,7 +37234,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="29" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="292"/>
       <c r="C29" s="292"/>
       <c r="D29" s="292"/>
@@ -37272,8 +37260,8 @@
       <c r="Z29" s="275"/>
       <c r="AA29" s="275"/>
     </row>
-    <row r="30" spans="2:31" ht="45" customHeight="1">
-      <c r="B30" s="459" t="s">
+    <row r="30" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="461" t="s">
         <v>122</v>
       </c>
       <c r="C30" s="285" t="s">
@@ -37329,8 +37317,8 @@
       </c>
       <c r="AE30" s="276"/>
     </row>
-    <row r="31" spans="2:31" ht="45" customHeight="1">
-      <c r="B31" s="460"/>
+    <row r="31" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="462"/>
       <c r="C31" s="285" t="s">
         <v>86</v>
       </c>
@@ -37383,8 +37371,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="2:31" ht="45" customHeight="1">
-      <c r="B32" s="460"/>
+    <row r="32" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="462"/>
       <c r="C32" s="285" t="s">
         <v>86</v>
       </c>
@@ -37439,8 +37427,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:31" ht="45" customHeight="1">
-      <c r="B33" s="460"/>
+    <row r="33" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="462"/>
       <c r="C33" s="285" t="s">
         <v>86</v>
       </c>
@@ -37495,7 +37483,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="34" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="292"/>
       <c r="C34" s="292"/>
       <c r="D34" s="292"/>
@@ -37521,8 +37509,8 @@
       <c r="Z34" s="275"/>
       <c r="AA34" s="275"/>
     </row>
-    <row r="35" spans="2:31" ht="45" customHeight="1">
-      <c r="B35" s="461" t="s">
+    <row r="35" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="463" t="s">
         <v>123</v>
       </c>
       <c r="C35" s="296" t="s">
@@ -37577,8 +37565,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" spans="2:31" ht="45" customHeight="1">
-      <c r="B36" s="462"/>
+    <row r="36" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="464"/>
       <c r="C36" s="296" t="s">
         <v>86</v>
       </c>
@@ -37631,8 +37619,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:31" ht="45" customHeight="1">
-      <c r="B37" s="462"/>
+    <row r="37" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="464"/>
       <c r="C37" s="296" t="s">
         <v>86</v>
       </c>
@@ -37687,8 +37675,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:31" ht="45" customHeight="1">
-      <c r="B38" s="462"/>
+    <row r="38" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="464"/>
       <c r="C38" s="296" t="s">
         <v>86</v>
       </c>
@@ -37743,7 +37731,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="39" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="292"/>
       <c r="C39" s="292"/>
       <c r="D39" s="292"/>
@@ -37769,8 +37757,8 @@
       <c r="Z39" s="275"/>
       <c r="AA39" s="275"/>
     </row>
-    <row r="40" spans="2:31" ht="45" customHeight="1">
-      <c r="B40" s="459" t="s">
+    <row r="40" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="461" t="s">
         <v>124</v>
       </c>
       <c r="C40" s="285" t="s">
@@ -37826,8 +37814,8 @@
       </c>
       <c r="AE40" s="276"/>
     </row>
-    <row r="41" spans="2:31" ht="45" customHeight="1">
-      <c r="B41" s="460"/>
+    <row r="41" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="462"/>
       <c r="C41" s="285" t="s">
         <v>86</v>
       </c>
@@ -37880,8 +37868,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="2:31" ht="45" customHeight="1">
-      <c r="B42" s="460"/>
+    <row r="42" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="462"/>
       <c r="C42" s="285" t="s">
         <v>86</v>
       </c>
@@ -37936,8 +37924,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="2:31" ht="45" customHeight="1">
-      <c r="B43" s="460"/>
+    <row r="43" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="462"/>
       <c r="C43" s="285" t="s">
         <v>86</v>
       </c>
@@ -37992,7 +37980,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="44" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="292"/>
       <c r="C44" s="292"/>
       <c r="D44" s="292"/>
@@ -38018,8 +38006,8 @@
       <c r="Z44" s="275"/>
       <c r="AA44" s="275"/>
     </row>
-    <row r="45" spans="2:31" ht="45" customHeight="1">
-      <c r="B45" s="461" t="s">
+    <row r="45" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="463" t="s">
         <v>125</v>
       </c>
       <c r="C45" s="296" t="s">
@@ -38074,8 +38062,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="2:31" ht="43.5" customHeight="1">
-      <c r="B46" s="462"/>
+    <row r="46" spans="2:31" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="464"/>
       <c r="C46" s="296" t="s">
         <v>125</v>
       </c>
@@ -38128,8 +38116,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="2:31" ht="58.5">
-      <c r="B47" s="470"/>
+    <row r="47" spans="2:31" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="B47" s="472"/>
       <c r="C47" s="296" t="s">
         <v>125</v>
       </c>
@@ -38184,7 +38172,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="48" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="292"/>
       <c r="C48" s="292"/>
       <c r="D48" s="292"/>
@@ -38210,7 +38198,7 @@
       <c r="Z48" s="275"/>
       <c r="AA48" s="275"/>
     </row>
-    <row r="49" spans="2:28" s="274" customFormat="1" ht="85.5" customHeight="1">
+    <row r="49" spans="2:28" s="274" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="303" t="s">
         <v>130</v>
       </c>
@@ -38266,7 +38254,7 @@
       </c>
       <c r="AA49" s="275"/>
     </row>
-    <row r="50" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="50" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="270"/>
       <c r="C50" s="270"/>
       <c r="D50" s="270"/>
@@ -38294,8 +38282,8 @@
       <c r="Z50" s="23"/>
       <c r="AA50" s="231"/>
     </row>
-    <row r="51" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B51" s="471" t="s">
+    <row r="51" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="473" t="s">
         <v>34</v>
       </c>
       <c r="C51" s="306" t="s">
@@ -38350,8 +38338,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="52" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B52" s="472"/>
+    <row r="52" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="474"/>
       <c r="C52" s="307" t="s">
         <v>135</v>
       </c>
@@ -38405,8 +38393,8 @@
       </c>
       <c r="AA52" s="274"/>
     </row>
-    <row r="53" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B53" s="472"/>
+    <row r="53" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="474"/>
       <c r="C53" s="307" t="s">
         <v>135</v>
       </c>
@@ -38459,8 +38447,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B54" s="472"/>
+    <row r="54" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="474"/>
       <c r="C54" s="307" t="s">
         <v>135</v>
       </c>
@@ -38513,8 +38501,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B55" s="473"/>
+    <row r="55" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="475"/>
       <c r="C55" s="308" t="s">
         <v>135</v>
       </c>
@@ -38567,7 +38555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1">
+    <row r="56" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="292"/>
       <c r="C56" s="292"/>
       <c r="D56" s="292"/>
@@ -38591,8 +38579,8 @@
       <c r="V56" s="292"/>
       <c r="W56" s="295"/>
     </row>
-    <row r="57" spans="2:28" ht="34.5" customHeight="1">
-      <c r="B57" s="463" t="s">
+    <row r="57" spans="2:28" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="465" t="s">
         <v>136</v>
       </c>
       <c r="C57" s="244" t="s">
@@ -38647,8 +38635,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" spans="2:28" ht="45.75" customHeight="1">
-      <c r="B58" s="464"/>
+    <row r="58" spans="2:28" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="466"/>
       <c r="C58" s="309" t="s">
         <v>136</v>
       </c>
@@ -38701,7 +38689,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="59" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="292"/>
       <c r="C59" s="292"/>
       <c r="D59" s="292"/>
@@ -38728,8 +38716,8 @@
       <c r="AA59" s="231"/>
       <c r="AB59" s="231"/>
     </row>
-    <row r="60" spans="2:28" ht="36" customHeight="1" thickBot="1">
-      <c r="B60" s="465" t="s">
+    <row r="60" spans="2:28" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="467" t="s">
         <v>139</v>
       </c>
       <c r="C60" s="310" t="s">
@@ -38786,8 +38774,8 @@
       <c r="AA60" s="275"/>
       <c r="AB60" s="275"/>
     </row>
-    <row r="61" spans="2:28" ht="36" customHeight="1" thickBot="1">
-      <c r="B61" s="466"/>
+    <row r="61" spans="2:28" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="468"/>
       <c r="C61" s="313" t="s">
         <v>139</v>
       </c>
@@ -38842,7 +38830,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="62" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="62" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="292"/>
       <c r="C62" s="292"/>
       <c r="D62" s="292"/>
@@ -38869,8 +38857,8 @@
       <c r="AA62" s="231"/>
       <c r="AB62" s="231"/>
     </row>
-    <row r="63" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B63" s="456" t="s">
+    <row r="63" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="458" t="s">
         <v>143</v>
       </c>
       <c r="C63" s="248" t="s">
@@ -38921,8 +38909,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B64" s="457"/>
+    <row r="64" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="459"/>
       <c r="C64" s="249" t="s">
         <v>91</v>
       </c>
@@ -38975,8 +38963,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B65" s="457"/>
+    <row r="65" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="459"/>
       <c r="C65" s="249" t="s">
         <v>91</v>
       </c>
@@ -39027,8 +39015,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="66" spans="2:28" ht="48" customHeight="1">
-      <c r="B66" s="457"/>
+    <row r="66" spans="2:28" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="459"/>
       <c r="C66" s="249" t="s">
         <v>91</v>
       </c>
@@ -39081,8 +39069,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="67" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B67" s="458"/>
+    <row r="67" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="460"/>
       <c r="C67" s="252" t="s">
         <v>91</v>
       </c>
@@ -39135,14 +39123,14 @@
         <v>154</v>
       </c>
     </row>
-    <row r="68" spans="2:28" ht="6.75" customHeight="1">
+    <row r="68" spans="2:28" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L68" s="316"/>
       <c r="M68" s="316"/>
       <c r="N68" s="316"/>
       <c r="Z68" s="231"/>
     </row>
-    <row r="69" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B69" s="467" t="s">
+    <row r="69" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="469" t="s">
         <v>155</v>
       </c>
       <c r="C69" s="317" t="s">
@@ -39197,8 +39185,8 @@
       <c r="AA69" s="275"/>
       <c r="AB69" s="275"/>
     </row>
-    <row r="70" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B70" s="468"/>
+    <row r="70" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="470"/>
       <c r="C70" s="319" t="s">
         <v>156</v>
       </c>
@@ -39249,8 +39237,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="71" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B71" s="468"/>
+    <row r="71" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="470"/>
       <c r="C71" s="319" t="s">
         <v>156</v>
       </c>
@@ -39303,8 +39291,8 @@
       <c r="AA71" s="275"/>
       <c r="AB71" s="275"/>
     </row>
-    <row r="72" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B72" s="468"/>
+    <row r="72" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="470"/>
       <c r="C72" s="319" t="s">
         <v>156</v>
       </c>
@@ -39355,8 +39343,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="73" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B73" s="468"/>
+    <row r="73" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="470"/>
       <c r="C73" s="319" t="s">
         <v>156</v>
       </c>
@@ -39407,8 +39395,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="2:28" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B74" s="469"/>
+    <row r="74" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="471"/>
       <c r="C74" s="322" t="s">
         <v>156</v>
       </c>
@@ -39459,14 +39447,14 @@
         <v>156</v>
       </c>
     </row>
-    <row r="75" spans="2:28">
+    <row r="75" spans="2:28" x14ac:dyDescent="0.25">
       <c r="L75" s="316">
         <v>0</v>
       </c>
       <c r="M75" s="316"/>
       <c r="N75" s="316"/>
     </row>
-    <row r="76" spans="2:28">
+    <row r="76" spans="2:28" x14ac:dyDescent="0.25">
       <c r="L76" s="316">
         <v>0</v>
       </c>
@@ -39521,7 +39509,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:AE85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.75" style="98" customWidth="1"/>
     <col min="2" max="2" width="16" style="98" customWidth="1"/>
@@ -39546,7 +39534,7 @@
     <col min="31" max="16384" width="9" style="98"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="5.45" customHeight="1">
+    <row r="1" spans="2:31" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="100"/>
       <c r="G1" s="100"/>
       <c r="H1" s="100"/>
@@ -39559,7 +39547,7 @@
       <c r="M1" s="101"/>
       <c r="O1" s="102"/>
     </row>
-    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1">
+    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="105"/>
       <c r="C2" s="105" t="s">
         <v>96</v>
@@ -39628,7 +39616,7 @@
       <c r="Z2" s="98"/>
       <c r="AB2" s="104"/>
     </row>
-    <row r="3" spans="2:31" ht="45" hidden="1" customHeight="1">
+    <row r="3" spans="2:31" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="114"/>
       <c r="C3" s="114"/>
       <c r="D3" s="115" t="s">
@@ -39668,7 +39656,7 @@
       <c r="Z3" s="98"/>
       <c r="AB3" s="104"/>
     </row>
-    <row r="4" spans="2:31" s="126" customFormat="1" ht="4.5" hidden="1" customHeight="1">
+    <row r="4" spans="2:31" s="126" customFormat="1" ht="4.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="122"/>
       <c r="C4" s="122"/>
       <c r="D4" s="122"/>
@@ -39696,8 +39684,8 @@
       <c r="AA4" s="127"/>
       <c r="AB4" s="127"/>
     </row>
-    <row r="5" spans="2:31" ht="45" customHeight="1">
-      <c r="B5" s="474" t="s">
+    <row r="5" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="476" t="s">
         <v>104</v>
       </c>
       <c r="C5" s="128" t="s">
@@ -39756,8 +39744,8 @@
       </c>
       <c r="AE5" s="137"/>
     </row>
-    <row r="6" spans="2:31" ht="45" customHeight="1">
-      <c r="B6" s="475"/>
+    <row r="6" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="477"/>
       <c r="C6" s="128" t="s">
         <v>86</v>
       </c>
@@ -39815,8 +39803,8 @@
       </c>
       <c r="AE6" s="137"/>
     </row>
-    <row r="7" spans="2:31" ht="113.25" customHeight="1">
-      <c r="B7" s="475"/>
+    <row r="7" spans="2:31" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="477"/>
       <c r="C7" s="128" t="s">
         <v>86</v>
       </c>
@@ -39864,8 +39852,8 @@
       </c>
       <c r="AE7" s="137"/>
     </row>
-    <row r="8" spans="2:31" ht="45" customHeight="1">
-      <c r="B8" s="475"/>
+    <row r="8" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="477"/>
       <c r="C8" s="128" t="s">
         <v>86</v>
       </c>
@@ -39925,8 +39913,8 @@
       </c>
       <c r="AE8" s="137"/>
     </row>
-    <row r="9" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B9" s="475"/>
+    <row r="9" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="477"/>
       <c r="C9" s="128" t="s">
         <v>86</v>
       </c>
@@ -39986,7 +39974,7 @@
       </c>
       <c r="AE9" s="137"/>
     </row>
-    <row r="10" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="10" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="122"/>
       <c r="C10" s="122"/>
       <c r="D10" s="122"/>
@@ -40018,8 +40006,8 @@
       </c>
       <c r="AE10" s="137"/>
     </row>
-    <row r="11" spans="2:31" ht="45" customHeight="1">
-      <c r="B11" s="480" t="s">
+    <row r="11" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="482" t="s">
         <v>168</v>
       </c>
       <c r="C11" s="141" t="s">
@@ -40075,8 +40063,8 @@
       </c>
       <c r="AE11" s="137"/>
     </row>
-    <row r="12" spans="2:31" ht="45" customHeight="1">
-      <c r="B12" s="481"/>
+    <row r="12" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="483"/>
       <c r="C12" s="141" t="s">
         <v>86</v>
       </c>
@@ -40130,8 +40118,8 @@
       </c>
       <c r="AB12" s="104"/>
     </row>
-    <row r="13" spans="2:31" ht="45" customHeight="1">
-      <c r="B13" s="481"/>
+    <row r="13" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="483"/>
       <c r="C13" s="141" t="s">
         <v>86</v>
       </c>
@@ -40187,8 +40175,8 @@
       </c>
       <c r="AB13" s="104"/>
     </row>
-    <row r="14" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B14" s="481"/>
+    <row r="14" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="483"/>
       <c r="C14" s="141" t="s">
         <v>86</v>
       </c>
@@ -40244,7 +40232,7 @@
       </c>
       <c r="AB14" s="104"/>
     </row>
-    <row r="15" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="15" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="122"/>
       <c r="C15" s="122"/>
       <c r="D15" s="122"/>
@@ -40272,8 +40260,8 @@
       <c r="Z15" s="275"/>
       <c r="AA15" s="127"/>
     </row>
-    <row r="16" spans="2:31" ht="45" customHeight="1">
-      <c r="B16" s="474" t="s">
+    <row r="16" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="476" t="s">
         <v>170</v>
       </c>
       <c r="C16" s="128" t="s">
@@ -40329,8 +40317,8 @@
       </c>
       <c r="AB16" s="104"/>
     </row>
-    <row r="17" spans="2:31" ht="45" customHeight="1">
-      <c r="B17" s="475"/>
+    <row r="17" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="477"/>
       <c r="C17" s="128" t="s">
         <v>86</v>
       </c>
@@ -40384,8 +40372,8 @@
       </c>
       <c r="AB17" s="104"/>
     </row>
-    <row r="18" spans="2:31" ht="45" customHeight="1">
-      <c r="B18" s="475"/>
+    <row r="18" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="477"/>
       <c r="C18" s="128" t="s">
         <v>86</v>
       </c>
@@ -40441,8 +40429,8 @@
       </c>
       <c r="AB18" s="104"/>
     </row>
-    <row r="19" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B19" s="475"/>
+    <row r="19" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="477"/>
       <c r="C19" s="128" t="s">
         <v>86</v>
       </c>
@@ -40498,7 +40486,7 @@
       </c>
       <c r="AB19" s="104"/>
     </row>
-    <row r="20" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="20" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="122"/>
       <c r="C20" s="122"/>
       <c r="D20" s="122"/>
@@ -40526,8 +40514,8 @@
       <c r="Z20" s="275"/>
       <c r="AA20" s="127"/>
     </row>
-    <row r="21" spans="2:31" ht="45" customHeight="1">
-      <c r="B21" s="480" t="s">
+    <row r="21" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="482" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="141" t="s">
@@ -40584,8 +40572,8 @@
       <c r="AB21" s="104"/>
       <c r="AE21" s="137"/>
     </row>
-    <row r="22" spans="2:31" ht="45" customHeight="1">
-      <c r="B22" s="481"/>
+    <row r="22" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="483"/>
       <c r="C22" s="141" t="s">
         <v>86</v>
       </c>
@@ -40639,8 +40627,8 @@
       </c>
       <c r="AB22" s="104"/>
     </row>
-    <row r="23" spans="2:31" ht="45" customHeight="1">
-      <c r="B23" s="481"/>
+    <row r="23" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="483"/>
       <c r="C23" s="141" t="s">
         <v>86</v>
       </c>
@@ -40696,8 +40684,8 @@
       </c>
       <c r="AB23" s="104"/>
     </row>
-    <row r="24" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B24" s="481"/>
+    <row r="24" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="483"/>
       <c r="C24" s="141" t="s">
         <v>86</v>
       </c>
@@ -40753,7 +40741,7 @@
       </c>
       <c r="AB24" s="104"/>
     </row>
-    <row r="25" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="25" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="122"/>
       <c r="C25" s="122"/>
       <c r="D25" s="122"/>
@@ -40781,8 +40769,8 @@
       <c r="Z25" s="275"/>
       <c r="AA25" s="127"/>
     </row>
-    <row r="26" spans="2:31" ht="45" customHeight="1">
-      <c r="B26" s="474" t="s">
+    <row r="26" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="476" t="s">
         <v>172</v>
       </c>
       <c r="C26" s="128" t="s">
@@ -40838,8 +40826,8 @@
       </c>
       <c r="AB26" s="104"/>
     </row>
-    <row r="27" spans="2:31" ht="45" customHeight="1">
-      <c r="B27" s="475"/>
+    <row r="27" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="477"/>
       <c r="C27" s="128" t="s">
         <v>86</v>
       </c>
@@ -40893,8 +40881,8 @@
       </c>
       <c r="AB27" s="104"/>
     </row>
-    <row r="28" spans="2:31" ht="45" customHeight="1">
-      <c r="B28" s="475"/>
+    <row r="28" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="477"/>
       <c r="C28" s="128" t="s">
         <v>86</v>
       </c>
@@ -40950,8 +40938,8 @@
       </c>
       <c r="AB28" s="104"/>
     </row>
-    <row r="29" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B29" s="475"/>
+    <row r="29" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="477"/>
       <c r="C29" s="128" t="s">
         <v>86</v>
       </c>
@@ -41007,7 +40995,7 @@
       </c>
       <c r="AB29" s="104"/>
     </row>
-    <row r="30" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="30" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="122"/>
       <c r="C30" s="122"/>
       <c r="D30" s="122"/>
@@ -41035,8 +41023,8 @@
       <c r="Z30" s="275"/>
       <c r="AA30" s="127"/>
     </row>
-    <row r="31" spans="2:31" ht="45" customHeight="1">
-      <c r="B31" s="480" t="s">
+    <row r="31" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="482" t="s">
         <v>173</v>
       </c>
       <c r="C31" s="141" t="s">
@@ -41093,8 +41081,8 @@
       <c r="AB31" s="104"/>
       <c r="AE31" s="137"/>
     </row>
-    <row r="32" spans="2:31" ht="45" customHeight="1">
-      <c r="B32" s="481"/>
+    <row r="32" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="483"/>
       <c r="C32" s="141" t="s">
         <v>86</v>
       </c>
@@ -41148,8 +41136,8 @@
       </c>
       <c r="AB32" s="104"/>
     </row>
-    <row r="33" spans="2:31" ht="45" customHeight="1">
-      <c r="B33" s="481"/>
+    <row r="33" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="483"/>
       <c r="C33" s="141" t="s">
         <v>86</v>
       </c>
@@ -41205,8 +41193,8 @@
       </c>
       <c r="AB33" s="104"/>
     </row>
-    <row r="34" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B34" s="481"/>
+    <row r="34" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="483"/>
       <c r="C34" s="141" t="s">
         <v>86</v>
       </c>
@@ -41262,7 +41250,7 @@
       </c>
       <c r="AB34" s="104"/>
     </row>
-    <row r="35" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="35" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="122"/>
       <c r="C35" s="122"/>
       <c r="D35" s="122"/>
@@ -41290,8 +41278,8 @@
       <c r="Z35" s="275"/>
       <c r="AA35" s="127"/>
     </row>
-    <row r="36" spans="2:31" ht="45" customHeight="1">
-      <c r="B36" s="474" t="s">
+    <row r="36" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="476" t="s">
         <v>174</v>
       </c>
       <c r="C36" s="128" t="s">
@@ -41347,8 +41335,8 @@
       </c>
       <c r="AB36" s="104"/>
     </row>
-    <row r="37" spans="2:31" ht="45" customHeight="1">
-      <c r="B37" s="475"/>
+    <row r="37" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="477"/>
       <c r="C37" s="128" t="s">
         <v>86</v>
       </c>
@@ -41402,8 +41390,8 @@
       </c>
       <c r="AB37" s="104"/>
     </row>
-    <row r="38" spans="2:31" ht="45" customHeight="1">
-      <c r="B38" s="475"/>
+    <row r="38" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="477"/>
       <c r="C38" s="128" t="s">
         <v>86</v>
       </c>
@@ -41459,8 +41447,8 @@
       </c>
       <c r="AB38" s="104"/>
     </row>
-    <row r="39" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B39" s="475"/>
+    <row r="39" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="477"/>
       <c r="C39" s="128" t="s">
         <v>86</v>
       </c>
@@ -41516,7 +41504,7 @@
       </c>
       <c r="AB39" s="104"/>
     </row>
-    <row r="40" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="40" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="122"/>
       <c r="C40" s="122"/>
       <c r="D40" s="122"/>
@@ -41544,8 +41532,8 @@
       <c r="Z40" s="275"/>
       <c r="AA40" s="127"/>
     </row>
-    <row r="41" spans="2:31" ht="45" customHeight="1">
-      <c r="B41" s="480" t="s">
+    <row r="41" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="482" t="s">
         <v>175</v>
       </c>
       <c r="C41" s="141" t="s">
@@ -41602,8 +41590,8 @@
       <c r="AB41" s="104"/>
       <c r="AE41" s="137"/>
     </row>
-    <row r="42" spans="2:31" ht="45" customHeight="1">
-      <c r="B42" s="481"/>
+    <row r="42" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="483"/>
       <c r="C42" s="141" t="s">
         <v>86</v>
       </c>
@@ -41657,8 +41645,8 @@
       </c>
       <c r="AB42" s="104"/>
     </row>
-    <row r="43" spans="2:31" ht="45" customHeight="1">
-      <c r="B43" s="481"/>
+    <row r="43" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="483"/>
       <c r="C43" s="141" t="s">
         <v>86</v>
       </c>
@@ -41714,8 +41702,8 @@
       </c>
       <c r="AB43" s="104"/>
     </row>
-    <row r="44" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B44" s="481"/>
+    <row r="44" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="483"/>
       <c r="C44" s="141" t="s">
         <v>86</v>
       </c>
@@ -41771,7 +41759,7 @@
       </c>
       <c r="AB44" s="104"/>
     </row>
-    <row r="45" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="45" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="122"/>
       <c r="C45" s="122"/>
       <c r="D45" s="122"/>
@@ -41799,8 +41787,8 @@
       <c r="Z45" s="127"/>
       <c r="AA45" s="127"/>
     </row>
-    <row r="46" spans="2:31" ht="45" customHeight="1">
-      <c r="B46" s="474" t="s">
+    <row r="46" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="476" t="s">
         <v>176</v>
       </c>
       <c r="C46" s="128" t="s">
@@ -41856,8 +41844,8 @@
       </c>
       <c r="AB46" s="104"/>
     </row>
-    <row r="47" spans="2:31" ht="45" customHeight="1">
-      <c r="B47" s="475"/>
+    <row r="47" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="477"/>
       <c r="C47" s="128" t="s">
         <v>86</v>
       </c>
@@ -41911,8 +41899,8 @@
       </c>
       <c r="AB47" s="104"/>
     </row>
-    <row r="48" spans="2:31" ht="45" customHeight="1">
-      <c r="B48" s="475"/>
+    <row r="48" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="477"/>
       <c r="C48" s="128" t="s">
         <v>86</v>
       </c>
@@ -41968,8 +41956,8 @@
       </c>
       <c r="AB48" s="104"/>
     </row>
-    <row r="49" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B49" s="475"/>
+    <row r="49" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="477"/>
       <c r="C49" s="128" t="s">
         <v>86</v>
       </c>
@@ -42025,7 +42013,7 @@
       </c>
       <c r="AB49" s="104"/>
     </row>
-    <row r="50" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="50" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="122"/>
       <c r="C50" s="122"/>
       <c r="D50" s="122"/>
@@ -42053,8 +42041,8 @@
       <c r="X50" s="160"/>
       <c r="AD50" s="98"/>
     </row>
-    <row r="51" spans="2:31" ht="45" customHeight="1">
-      <c r="B51" s="480" t="s">
+    <row r="51" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="482" t="s">
         <v>177</v>
       </c>
       <c r="C51" s="141" t="s">
@@ -42111,8 +42099,8 @@
       <c r="AB51" s="104"/>
       <c r="AE51" s="137"/>
     </row>
-    <row r="52" spans="2:31" ht="45" customHeight="1">
-      <c r="B52" s="481"/>
+    <row r="52" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="483"/>
       <c r="C52" s="141" t="s">
         <v>86</v>
       </c>
@@ -42166,8 +42154,8 @@
       </c>
       <c r="AB52" s="104"/>
     </row>
-    <row r="53" spans="2:31" ht="45" customHeight="1">
-      <c r="B53" s="481"/>
+    <row r="53" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="483"/>
       <c r="C53" s="141" t="s">
         <v>86</v>
       </c>
@@ -42223,8 +42211,8 @@
       </c>
       <c r="AB53" s="104"/>
     </row>
-    <row r="54" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B54" s="481"/>
+    <row r="54" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B54" s="483"/>
       <c r="C54" s="141" t="s">
         <v>86</v>
       </c>
@@ -42280,7 +42268,7 @@
       </c>
       <c r="AB54" s="104"/>
     </row>
-    <row r="55" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="55" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="122"/>
       <c r="C55" s="122"/>
       <c r="D55" s="122"/>
@@ -42308,8 +42296,8 @@
       <c r="X55" s="160"/>
       <c r="AD55" s="98"/>
     </row>
-    <row r="56" spans="2:31" ht="45" customHeight="1">
-      <c r="B56" s="474" t="s">
+    <row r="56" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="476" t="s">
         <v>125</v>
       </c>
       <c r="C56" s="128" t="s">
@@ -42363,8 +42351,8 @@
       </c>
       <c r="AB56" s="104"/>
     </row>
-    <row r="57" spans="2:31" ht="43.5" customHeight="1">
-      <c r="B57" s="475"/>
+    <row r="57" spans="2:31" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="477"/>
       <c r="C57" s="128" t="s">
         <v>125</v>
       </c>
@@ -42416,8 +42404,8 @@
       </c>
       <c r="AB57" s="104"/>
     </row>
-    <row r="58" spans="2:31" ht="51.75">
-      <c r="B58" s="476"/>
+    <row r="58" spans="2:31" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="478"/>
       <c r="C58" s="128" t="s">
         <v>125</v>
       </c>
@@ -42471,7 +42459,7 @@
       </c>
       <c r="AB58" s="104"/>
     </row>
-    <row r="59" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="59" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="122"/>
       <c r="C59" s="122"/>
       <c r="D59" s="122"/>
@@ -42499,7 +42487,7 @@
       <c r="Z59" s="275"/>
       <c r="AA59" s="127"/>
     </row>
-    <row r="60" spans="2:31" s="126" customFormat="1" ht="85.5" customHeight="1" thickBot="1">
+    <row r="60" spans="2:31" s="126" customFormat="1" ht="85.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="172" t="s">
         <v>130</v>
       </c>
@@ -42555,7 +42543,7 @@
       </c>
       <c r="AA60" s="127"/>
     </row>
-    <row r="61" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1">
+    <row r="61" spans="2:31" s="126" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="168"/>
       <c r="C61" s="168"/>
       <c r="D61" s="168"/>
@@ -42583,8 +42571,8 @@
       <c r="Z61" s="23"/>
       <c r="AA61" s="104"/>
     </row>
-    <row r="62" spans="2:31" ht="28.9" customHeight="1">
-      <c r="B62" s="477" t="s">
+    <row r="62" spans="2:31" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="479" t="s">
         <v>181</v>
       </c>
       <c r="C62" s="182" t="s">
@@ -42638,8 +42626,8 @@
       </c>
       <c r="AB62" s="104"/>
     </row>
-    <row r="63" spans="2:31" ht="28.9" customHeight="1">
-      <c r="B63" s="478"/>
+    <row r="63" spans="2:31" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="480"/>
       <c r="C63" s="191" t="s">
         <v>135</v>
       </c>
@@ -42692,8 +42680,8 @@
       <c r="AA63" s="126"/>
       <c r="AB63" s="104"/>
     </row>
-    <row r="64" spans="2:31" ht="28.9" customHeight="1">
-      <c r="B64" s="478"/>
+    <row r="64" spans="2:31" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="480"/>
       <c r="C64" s="191" t="s">
         <v>135</v>
       </c>
@@ -42747,8 +42735,8 @@
       </c>
       <c r="AB64" s="104"/>
     </row>
-    <row r="65" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B65" s="478"/>
+    <row r="65" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="480"/>
       <c r="C65" s="191" t="s">
         <v>135</v>
       </c>
@@ -42800,8 +42788,8 @@
       </c>
       <c r="AB65" s="104"/>
     </row>
-    <row r="66" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B66" s="479"/>
+    <row r="66" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="481"/>
       <c r="C66" s="193" t="s">
         <v>135</v>
       </c>
@@ -42853,7 +42841,7 @@
       </c>
       <c r="AB66" s="104"/>
     </row>
-    <row r="67" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1">
+    <row r="67" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="122"/>
       <c r="C67" s="122"/>
       <c r="D67" s="122"/>
@@ -42880,8 +42868,8 @@
       <c r="W67" s="125"/>
       <c r="Z67" s="274"/>
     </row>
-    <row r="68" spans="2:28" ht="34.5" customHeight="1">
-      <c r="B68" s="482" t="s">
+    <row r="68" spans="2:28" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="484" t="s">
         <v>136</v>
       </c>
       <c r="C68" s="202" t="s">
@@ -42935,8 +42923,8 @@
       </c>
       <c r="AB68" s="104"/>
     </row>
-    <row r="69" spans="2:28" ht="45.75" customHeight="1">
-      <c r="B69" s="483"/>
+    <row r="69" spans="2:28" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="485"/>
       <c r="C69" s="209" t="s">
         <v>136</v>
       </c>
@@ -42988,7 +42976,7 @@
       </c>
       <c r="AB69" s="104"/>
     </row>
-    <row r="70" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1">
+    <row r="70" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="122"/>
       <c r="C70" s="122"/>
       <c r="D70" s="122"/>
@@ -43017,8 +43005,8 @@
       <c r="AA70" s="104"/>
       <c r="AB70" s="104"/>
     </row>
-    <row r="71" spans="2:28" ht="51.75" customHeight="1">
-      <c r="B71" s="484" t="s">
+    <row r="71" spans="2:28" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="486" t="s">
         <v>139</v>
       </c>
       <c r="C71" s="217" t="s">
@@ -43073,8 +43061,8 @@
       <c r="AA71" s="127"/>
       <c r="AB71" s="127"/>
     </row>
-    <row r="72" spans="2:28" ht="51" customHeight="1">
-      <c r="B72" s="485"/>
+    <row r="72" spans="2:28" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="487"/>
       <c r="C72" s="222" t="s">
         <v>139</v>
       </c>
@@ -43128,7 +43116,7 @@
       </c>
       <c r="AB72" s="104"/>
     </row>
-    <row r="73" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1">
+    <row r="73" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="168"/>
       <c r="C73" s="168"/>
       <c r="D73" s="168"/>
@@ -43157,11 +43145,11 @@
       <c r="AA73" s="104"/>
       <c r="AB73" s="104"/>
     </row>
-    <row r="74" spans="2:28" s="230" customFormat="1" ht="38.25" customHeight="1">
-      <c r="B74" s="486" t="s">
+    <row r="74" spans="2:28" s="230" customFormat="1" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="488" t="s">
         <v>143</v>
       </c>
-      <c r="C74" s="489" t="s">
+      <c r="C74" s="416" t="s">
         <v>91</v>
       </c>
       <c r="D74" s="69" t="s">
@@ -43211,9 +43199,11 @@
       <c r="AA74" s="231"/>
       <c r="AB74" s="231"/>
     </row>
-    <row r="75" spans="2:28" ht="38.25" customHeight="1">
-      <c r="B75" s="487"/>
-      <c r="C75" s="490"/>
+    <row r="75" spans="2:28" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="489"/>
+      <c r="C75" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D75" s="232" t="s">
         <v>186</v>
       </c>
@@ -43264,9 +43254,11 @@
       </c>
       <c r="AB75" s="104"/>
     </row>
-    <row r="76" spans="2:28" ht="38.25" customHeight="1">
-      <c r="B76" s="487"/>
-      <c r="C76" s="490"/>
+    <row r="76" spans="2:28" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="489"/>
+      <c r="C76" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D76" s="232" t="s">
         <v>7</v>
       </c>
@@ -43315,9 +43307,11 @@
       </c>
       <c r="AB76" s="104"/>
     </row>
-    <row r="77" spans="2:28" ht="66" customHeight="1">
-      <c r="B77" s="487"/>
-      <c r="C77" s="490"/>
+    <row r="77" spans="2:28" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="489"/>
+      <c r="C77" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D77" s="232" t="s">
         <v>187</v>
       </c>
@@ -43368,9 +43362,11 @@
       </c>
       <c r="AB77" s="104"/>
     </row>
-    <row r="78" spans="2:28" ht="38.25" customHeight="1">
-      <c r="B78" s="488"/>
-      <c r="C78" s="491"/>
+    <row r="78" spans="2:28" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="490"/>
+      <c r="C78" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D78" s="215" t="s">
         <v>152</v>
       </c>
@@ -43421,7 +43417,7 @@
       </c>
       <c r="AB78" s="104"/>
     </row>
-    <row r="79" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1">
+    <row r="79" spans="2:28" s="126" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="253"/>
       <c r="C79" s="253"/>
       <c r="D79" s="253"/>
@@ -43450,11 +43446,11 @@
       <c r="AA79" s="104"/>
       <c r="AB79" s="104"/>
     </row>
-    <row r="80" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B80" s="484" t="s">
+    <row r="80" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="486" t="s">
         <v>155</v>
       </c>
-      <c r="C80" s="492" t="s">
+      <c r="C80" s="417" t="s">
         <v>156</v>
       </c>
       <c r="D80" s="234" t="s">
@@ -43506,9 +43502,11 @@
       <c r="AA80" s="127"/>
       <c r="AB80" s="127"/>
     </row>
-    <row r="81" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B81" s="495"/>
-      <c r="C81" s="493"/>
+    <row r="81" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="491"/>
+      <c r="C81" s="417" t="s">
+        <v>156</v>
+      </c>
       <c r="D81" s="236" t="s">
         <v>158</v>
       </c>
@@ -43557,9 +43555,11 @@
       </c>
       <c r="AB81" s="104"/>
     </row>
-    <row r="82" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B82" s="495"/>
-      <c r="C82" s="493"/>
+    <row r="82" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="491"/>
+      <c r="C82" s="417" t="s">
+        <v>156</v>
+      </c>
       <c r="D82" s="236" t="s">
         <v>159</v>
       </c>
@@ -43609,9 +43609,11 @@
       <c r="AA82" s="127"/>
       <c r="AB82" s="127"/>
     </row>
-    <row r="83" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B83" s="495"/>
-      <c r="C83" s="493"/>
+    <row r="83" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="491"/>
+      <c r="C83" s="417" t="s">
+        <v>156</v>
+      </c>
       <c r="D83" s="236" t="s">
         <v>160</v>
       </c>
@@ -43660,9 +43662,11 @@
       </c>
       <c r="AB83" s="104"/>
     </row>
-    <row r="84" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B84" s="495"/>
-      <c r="C84" s="493"/>
+    <row r="84" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="491"/>
+      <c r="C84" s="417" t="s">
+        <v>156</v>
+      </c>
       <c r="D84" s="236" t="s">
         <v>46</v>
       </c>
@@ -43711,9 +43715,11 @@
       </c>
       <c r="AB84" s="104"/>
     </row>
-    <row r="85" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B85" s="485"/>
-      <c r="C85" s="494"/>
+    <row r="85" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="487"/>
+      <c r="C85" s="417" t="s">
+        <v>156</v>
+      </c>
       <c r="D85" s="240" t="s">
         <v>161</v>
       </c>
@@ -43763,12 +43769,10 @@
       <c r="AB85" s="104"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="B68:B69"/>
     <mergeCell ref="B71:B72"/>
     <mergeCell ref="B74:B78"/>
-    <mergeCell ref="C74:C78"/>
-    <mergeCell ref="C80:C85"/>
     <mergeCell ref="B80:B85"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B11:B14"/>
@@ -43823,7 +43827,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:AE75"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.25" style="230" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.875" style="230" bestFit="1" customWidth="1"/>
@@ -43857,7 +43861,7 @@
     <col min="30" max="16384" width="9" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="5.45" customHeight="1">
+    <row r="1" spans="1:31" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="230" t="s">
         <v>188</v>
       </c>
@@ -43873,7 +43877,7 @@
       <c r="M1" s="258"/>
       <c r="O1" s="259"/>
     </row>
-    <row r="2" spans="1:31" ht="24" customHeight="1" thickBot="1">
+    <row r="2" spans="1:31" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="261"/>
       <c r="C2" s="261" t="s">
         <v>96</v>
@@ -43940,7 +43944,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="45" hidden="1" customHeight="1">
+    <row r="3" spans="1:31" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="262"/>
       <c r="C3" s="262"/>
       <c r="D3" s="263" t="s">
@@ -43976,7 +43980,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="274" customFormat="1" ht="4.5" hidden="1" customHeight="1">
+    <row r="4" spans="1:31" s="274" customFormat="1" ht="4.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="292"/>
       <c r="C4" s="292"/>
       <c r="D4" s="292"/>
@@ -44004,8 +44008,8 @@
       <c r="AA4" s="275"/>
       <c r="AB4" s="275"/>
     </row>
-    <row r="5" spans="1:31" ht="45" customHeight="1">
-      <c r="B5" s="461" t="s">
+    <row r="5" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="463" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="296" t="s">
@@ -44063,8 +44067,8 @@
       </c>
       <c r="AE5" s="276"/>
     </row>
-    <row r="6" spans="1:31" ht="45" customHeight="1">
-      <c r="B6" s="462"/>
+    <row r="6" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="464"/>
       <c r="C6" s="296" t="s">
         <v>86</v>
       </c>
@@ -44121,8 +44125,8 @@
       </c>
       <c r="AE6" s="276"/>
     </row>
-    <row r="7" spans="1:31" ht="111.75" customHeight="1">
-      <c r="B7" s="462"/>
+    <row r="7" spans="1:31" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="464"/>
       <c r="C7" s="296" t="s">
         <v>86</v>
       </c>
@@ -44169,8 +44173,8 @@
       </c>
       <c r="AE7" s="276"/>
     </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1">
-      <c r="B8" s="462"/>
+    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="464"/>
       <c r="C8" s="296" t="s">
         <v>86</v>
       </c>
@@ -44229,8 +44233,8 @@
       </c>
       <c r="AE8" s="276"/>
     </row>
-    <row r="9" spans="1:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B9" s="462"/>
+    <row r="9" spans="1:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="464"/>
       <c r="C9" s="296" t="s">
         <v>86</v>
       </c>
@@ -44289,7 +44293,7 @@
       </c>
       <c r="AE9" s="276"/>
     </row>
-    <row r="10" spans="1:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="10" spans="1:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="292"/>
       <c r="C10" s="292"/>
       <c r="D10" s="292" t="s">
@@ -44323,8 +44327,8 @@
       </c>
       <c r="AE10" s="276"/>
     </row>
-    <row r="11" spans="1:31" ht="45" customHeight="1">
-      <c r="B11" s="459" t="s">
+    <row r="11" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="461" t="s">
         <v>196</v>
       </c>
       <c r="C11" s="285" t="s">
@@ -44381,8 +44385,8 @@
       </c>
       <c r="AE11" s="276"/>
     </row>
-    <row r="12" spans="1:31" ht="45" customHeight="1">
-      <c r="B12" s="460"/>
+    <row r="12" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="462"/>
       <c r="C12" s="285" t="s">
         <v>86</v>
       </c>
@@ -44437,8 +44441,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="45" customHeight="1">
-      <c r="B13" s="460"/>
+    <row r="13" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="462"/>
       <c r="C13" s="285" t="s">
         <v>86</v>
       </c>
@@ -44491,8 +44495,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B14" s="460"/>
+    <row r="14" spans="1:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="462"/>
       <c r="C14" s="285" t="s">
         <v>86</v>
       </c>
@@ -44545,7 +44549,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="15" spans="1:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="292"/>
       <c r="C15" s="292"/>
       <c r="D15" s="292" t="s">
@@ -44575,8 +44579,8 @@
       <c r="Z15" s="275"/>
       <c r="AA15" s="275"/>
     </row>
-    <row r="16" spans="1:31" ht="45" customHeight="1">
-      <c r="B16" s="461" t="s">
+    <row r="16" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="463" t="s">
         <v>118</v>
       </c>
       <c r="C16" s="296" t="s">
@@ -44631,8 +44635,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="2:31" ht="45" customHeight="1">
-      <c r="B17" s="462"/>
+    <row r="17" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="464"/>
       <c r="C17" s="296" t="s">
         <v>86</v>
       </c>
@@ -44685,8 +44689,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:31" ht="45" customHeight="1">
-      <c r="B18" s="462"/>
+    <row r="18" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="464"/>
       <c r="C18" s="296" t="s">
         <v>86</v>
       </c>
@@ -44739,8 +44743,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B19" s="462"/>
+    <row r="19" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="464"/>
       <c r="C19" s="296" t="s">
         <v>86</v>
       </c>
@@ -44793,7 +44797,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="20" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="292"/>
       <c r="C20" s="292"/>
       <c r="D20" s="292" t="s">
@@ -44823,8 +44827,8 @@
       <c r="Z20" s="275"/>
       <c r="AA20" s="275"/>
     </row>
-    <row r="21" spans="2:31" ht="45" customHeight="1">
-      <c r="B21" s="459" t="s">
+    <row r="21" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="461" t="s">
         <v>171</v>
       </c>
       <c r="C21" s="285" t="s">
@@ -44880,8 +44884,8 @@
       </c>
       <c r="AE21" s="276"/>
     </row>
-    <row r="22" spans="2:31" ht="45" customHeight="1">
-      <c r="B22" s="460"/>
+    <row r="22" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="462"/>
       <c r="C22" s="285" t="s">
         <v>86</v>
       </c>
@@ -44934,8 +44938,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:31" ht="45" customHeight="1">
-      <c r="B23" s="460"/>
+    <row r="23" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="462"/>
       <c r="C23" s="285" t="s">
         <v>86</v>
       </c>
@@ -44988,8 +44992,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B24" s="460"/>
+    <row r="24" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="462"/>
       <c r="C24" s="285" t="s">
         <v>86</v>
       </c>
@@ -45042,7 +45046,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="25" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="292"/>
       <c r="C25" s="292"/>
       <c r="D25" s="292" t="s">
@@ -45072,8 +45076,8 @@
       <c r="Z25" s="275"/>
       <c r="AA25" s="275"/>
     </row>
-    <row r="26" spans="2:31" ht="45" customHeight="1">
-      <c r="B26" s="461" t="s">
+    <row r="26" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="463" t="s">
         <v>197</v>
       </c>
       <c r="C26" s="296" t="s">
@@ -45128,8 +45132,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="2:31" ht="45" customHeight="1">
-      <c r="B27" s="462"/>
+    <row r="27" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="464"/>
       <c r="C27" s="296" t="s">
         <v>86</v>
       </c>
@@ -45182,8 +45186,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:31" ht="45" customHeight="1">
-      <c r="B28" s="462"/>
+    <row r="28" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="464"/>
       <c r="C28" s="296" t="s">
         <v>86</v>
       </c>
@@ -45236,8 +45240,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B29" s="462"/>
+    <row r="29" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="464"/>
       <c r="C29" s="296" t="s">
         <v>86</v>
       </c>
@@ -45290,7 +45294,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="30" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="292"/>
       <c r="C30" s="292"/>
       <c r="D30" s="292" t="s">
@@ -45320,8 +45324,8 @@
       <c r="Z30" s="275"/>
       <c r="AA30" s="275"/>
     </row>
-    <row r="31" spans="2:31" ht="45" customHeight="1">
-      <c r="B31" s="459" t="s">
+    <row r="31" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="461" t="s">
         <v>198</v>
       </c>
       <c r="C31" s="285" t="s">
@@ -45377,8 +45381,8 @@
       </c>
       <c r="AE31" s="276"/>
     </row>
-    <row r="32" spans="2:31" ht="45" customHeight="1">
-      <c r="B32" s="460"/>
+    <row r="32" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="462"/>
       <c r="C32" s="285" t="s">
         <v>86</v>
       </c>
@@ -45431,8 +45435,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:31" ht="45" customHeight="1">
-      <c r="B33" s="460"/>
+    <row r="33" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="462"/>
       <c r="C33" s="285" t="s">
         <v>86</v>
       </c>
@@ -45485,8 +45489,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B34" s="460"/>
+    <row r="34" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="462"/>
       <c r="C34" s="285" t="s">
         <v>86</v>
       </c>
@@ -45539,7 +45543,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="35" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="292"/>
       <c r="C35" s="292"/>
       <c r="D35" s="292" t="s">
@@ -45569,8 +45573,8 @@
       <c r="Z35" s="275"/>
       <c r="AA35" s="275"/>
     </row>
-    <row r="36" spans="2:31" ht="45" customHeight="1">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="463" t="s">
         <v>199</v>
       </c>
       <c r="C36" s="296" t="s">
@@ -45625,8 +45629,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" spans="2:31" ht="45" customHeight="1">
-      <c r="B37" s="462"/>
+    <row r="37" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="464"/>
       <c r="C37" s="296" t="s">
         <v>86</v>
       </c>
@@ -45679,8 +45683,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:31" ht="45" customHeight="1">
-      <c r="B38" s="462"/>
+    <row r="38" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="464"/>
       <c r="C38" s="296" t="s">
         <v>86</v>
       </c>
@@ -45733,8 +45737,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B39" s="462"/>
+    <row r="39" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="464"/>
       <c r="C39" s="296" t="s">
         <v>86</v>
       </c>
@@ -45787,7 +45791,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="40" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="292"/>
       <c r="C40" s="292"/>
       <c r="D40" s="292" t="s">
@@ -45817,8 +45821,8 @@
       <c r="Z40" s="275"/>
       <c r="AA40" s="275"/>
     </row>
-    <row r="41" spans="2:31" ht="45" customHeight="1">
-      <c r="B41" s="459" t="s">
+    <row r="41" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="461" t="s">
         <v>200</v>
       </c>
       <c r="C41" s="285" t="s">
@@ -45874,8 +45878,8 @@
       </c>
       <c r="AE41" s="276"/>
     </row>
-    <row r="42" spans="2:31" ht="45" customHeight="1">
-      <c r="B42" s="460"/>
+    <row r="42" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="462"/>
       <c r="C42" s="285" t="s">
         <v>86</v>
       </c>
@@ -45928,8 +45932,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="2:31" ht="45" customHeight="1">
-      <c r="B43" s="460"/>
+    <row r="43" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="462"/>
       <c r="C43" s="285" t="s">
         <v>86</v>
       </c>
@@ -45982,8 +45986,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B44" s="460"/>
+    <row r="44" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="462"/>
       <c r="C44" s="285" t="s">
         <v>86</v>
       </c>
@@ -46036,7 +46040,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="45" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="292"/>
       <c r="C45" s="292"/>
       <c r="D45" s="292"/>
@@ -46064,8 +46068,8 @@
       <c r="Z45" s="275"/>
       <c r="AA45" s="275"/>
     </row>
-    <row r="46" spans="2:31" ht="57.75">
-      <c r="B46" s="461" t="s">
+    <row r="46" spans="2:31" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="463" t="s">
         <v>125</v>
       </c>
       <c r="C46" s="296" t="s">
@@ -46118,8 +46122,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="2:31" ht="57.75">
-      <c r="B47" s="462"/>
+    <row r="47" spans="2:31" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="464"/>
       <c r="C47" s="296" t="s">
         <v>125</v>
       </c>
@@ -46170,8 +46174,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="2:31" ht="58.5" thickBot="1">
-      <c r="B48" s="470"/>
+    <row r="48" spans="2:31" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="472"/>
       <c r="C48" s="296" t="s">
         <v>125</v>
       </c>
@@ -46224,7 +46228,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="49" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="292"/>
       <c r="C49" s="292"/>
       <c r="D49" s="292"/>
@@ -46252,7 +46256,7 @@
       <c r="Z49" s="275"/>
       <c r="AA49" s="275"/>
     </row>
-    <row r="50" spans="2:28" s="274" customFormat="1" ht="85.5" customHeight="1" thickBot="1">
+    <row r="50" spans="2:28" s="274" customFormat="1" ht="85.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="303" t="s">
         <v>130</v>
       </c>
@@ -46308,7 +46312,7 @@
       </c>
       <c r="AA50" s="275"/>
     </row>
-    <row r="51" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="51" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B51" s="270"/>
       <c r="C51" s="270"/>
       <c r="D51" s="270"/>
@@ -46336,8 +46340,8 @@
       <c r="Z51" s="23"/>
       <c r="AA51" s="231"/>
     </row>
-    <row r="52" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B52" s="471" t="s">
+    <row r="52" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="473" t="s">
         <v>34</v>
       </c>
       <c r="C52" s="306" t="s">
@@ -46390,8 +46394,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="53" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B53" s="472"/>
+    <row r="53" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="474"/>
       <c r="C53" s="307" t="s">
         <v>135</v>
       </c>
@@ -46443,8 +46447,8 @@
       </c>
       <c r="AA53" s="274"/>
     </row>
-    <row r="54" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B54" s="472"/>
+    <row r="54" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="474"/>
       <c r="C54" s="307" t="s">
         <v>135</v>
       </c>
@@ -46495,8 +46499,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="55" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B55" s="472"/>
+    <row r="55" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="474"/>
       <c r="C55" s="307" t="s">
         <v>135</v>
       </c>
@@ -46547,8 +46551,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B56" s="473"/>
+    <row r="56" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="475"/>
       <c r="C56" s="308" t="s">
         <v>135</v>
       </c>
@@ -46599,7 +46603,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="57" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="292"/>
       <c r="C57" s="292"/>
       <c r="D57" s="292"/>
@@ -46625,8 +46629,8 @@
       <c r="V57" s="292"/>
       <c r="W57" s="295"/>
     </row>
-    <row r="58" spans="2:28" ht="34.5" customHeight="1">
-      <c r="B58" s="463" t="s">
+    <row r="58" spans="2:28" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="465" t="s">
         <v>136</v>
       </c>
       <c r="C58" s="244" t="s">
@@ -46677,8 +46681,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="59" spans="2:28" ht="45.75" customHeight="1" thickBot="1">
-      <c r="B59" s="464"/>
+    <row r="59" spans="2:28" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B59" s="466"/>
       <c r="C59" s="309" t="s">
         <v>136</v>
       </c>
@@ -46729,7 +46733,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="60" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="60" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="292"/>
       <c r="C60" s="292"/>
       <c r="D60" s="292"/>
@@ -46758,8 +46762,8 @@
       <c r="AA60" s="231"/>
       <c r="AB60" s="231"/>
     </row>
-    <row r="61" spans="2:28" ht="126">
-      <c r="B61" s="467" t="s">
+    <row r="61" spans="2:28" ht="126" x14ac:dyDescent="0.25">
+      <c r="B61" s="469" t="s">
         <v>139</v>
       </c>
       <c r="C61" s="317" t="s">
@@ -46814,8 +46818,8 @@
       <c r="AA61" s="275"/>
       <c r="AB61" s="275"/>
     </row>
-    <row r="62" spans="2:28" ht="36" customHeight="1" thickBot="1">
-      <c r="B62" s="469"/>
+    <row r="62" spans="2:28" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B62" s="471"/>
       <c r="C62" s="322" t="s">
         <v>139</v>
       </c>
@@ -46868,7 +46872,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="63" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="63" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="292"/>
       <c r="C63" s="292"/>
       <c r="D63" s="292"/>
@@ -46897,11 +46901,11 @@
       <c r="AA63" s="231"/>
       <c r="AB63" s="231"/>
     </row>
-    <row r="64" spans="2:28" ht="25.5" customHeight="1">
-      <c r="B64" s="456" t="s">
+    <row r="64" spans="2:28" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B64" s="458" t="s">
         <v>143</v>
       </c>
-      <c r="C64" s="489" t="s">
+      <c r="C64" s="416" t="s">
         <v>91</v>
       </c>
       <c r="D64" s="69" t="s">
@@ -46949,9 +46953,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B65" s="457"/>
-      <c r="C65" s="490"/>
+    <row r="65" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="459"/>
+      <c r="C65" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D65" s="93" t="s">
         <v>203</v>
       </c>
@@ -47001,9 +47007,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="66" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B66" s="457"/>
-      <c r="C66" s="490"/>
+    <row r="66" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="459"/>
+      <c r="C66" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D66" s="93" t="s">
         <v>7</v>
       </c>
@@ -47051,9 +47059,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="67" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B67" s="457"/>
-      <c r="C67" s="490"/>
+    <row r="67" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B67" s="459"/>
+      <c r="C67" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D67" s="93" t="s">
         <v>204</v>
       </c>
@@ -47103,9 +47113,11 @@
         <v>151</v>
       </c>
     </row>
-    <row r="68" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B68" s="458"/>
-      <c r="C68" s="491"/>
+    <row r="68" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="460"/>
+      <c r="C68" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D68" s="95" t="s">
         <v>205</v>
       </c>
@@ -47155,7 +47167,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="69" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="69" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="292"/>
       <c r="C69" s="292"/>
       <c r="D69" s="292"/>
@@ -47184,8 +47196,8 @@
       <c r="AA69" s="231"/>
       <c r="AB69" s="231"/>
     </row>
-    <row r="70" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B70" s="465" t="s">
+    <row r="70" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="467" t="s">
         <v>155</v>
       </c>
       <c r="C70" s="310" t="s">
@@ -47240,8 +47252,8 @@
       <c r="AA70" s="275"/>
       <c r="AB70" s="275"/>
     </row>
-    <row r="71" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B71" s="496"/>
+    <row r="71" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="492"/>
       <c r="C71" s="325" t="s">
         <v>156</v>
       </c>
@@ -47292,8 +47304,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="72" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B72" s="496"/>
+    <row r="72" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="492"/>
       <c r="C72" s="325" t="s">
         <v>156</v>
       </c>
@@ -47346,8 +47358,8 @@
       <c r="AA72" s="275"/>
       <c r="AB72" s="275"/>
     </row>
-    <row r="73" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B73" s="496"/>
+    <row r="73" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="492"/>
       <c r="C73" s="325" t="s">
         <v>156</v>
       </c>
@@ -47398,8 +47410,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B74" s="496"/>
+    <row r="74" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="492"/>
       <c r="C74" s="325" t="s">
         <v>156</v>
       </c>
@@ -47450,8 +47462,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="75" spans="2:28" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B75" s="466"/>
+    <row r="75" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="468"/>
       <c r="C75" s="313" t="s">
         <v>156</v>
       </c>
@@ -47503,10 +47515,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B70:B75"/>
     <mergeCell ref="B64:B68"/>
-    <mergeCell ref="C64:C68"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B16:B19"/>
@@ -47557,7 +47568,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B1:AF88"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.75" style="230" customWidth="1"/>
     <col min="2" max="2" width="16" style="230" customWidth="1"/>
@@ -47587,7 +47598,7 @@
     <col min="32" max="16384" width="9" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:32" ht="5.45" customHeight="1">
+    <row r="1" spans="2:32" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="257"/>
       <c r="G1" s="257"/>
       <c r="H1" s="257"/>
@@ -47601,7 +47612,7 @@
       <c r="N1" s="259"/>
       <c r="P1" s="346"/>
     </row>
-    <row r="2" spans="2:32" ht="24" customHeight="1" thickBot="1">
+    <row r="2" spans="2:32" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="261"/>
       <c r="C2" s="261" t="s">
         <v>96</v>
@@ -47669,7 +47680,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:32" ht="45" hidden="1" customHeight="1">
+    <row r="3" spans="2:32" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="262"/>
       <c r="C3" s="262"/>
       <c r="D3" s="263" t="s">
@@ -47714,7 +47725,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="2:32" s="274" customFormat="1" ht="4.5" hidden="1" customHeight="1">
+    <row r="4" spans="2:32" s="274" customFormat="1" ht="4.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="292"/>
       <c r="C4" s="292"/>
       <c r="D4" s="292"/>
@@ -47743,8 +47754,8 @@
       <c r="AB4" s="275"/>
       <c r="AC4" s="275"/>
     </row>
-    <row r="5" spans="2:32" ht="60.75">
-      <c r="B5" s="461" t="s">
+    <row r="5" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="463" t="s">
         <v>191</v>
       </c>
       <c r="C5" s="332" t="s">
@@ -47808,8 +47819,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="6" spans="2:32" ht="60.75">
-      <c r="B6" s="462"/>
+    <row r="6" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="464"/>
       <c r="C6" s="296" t="s">
         <v>86</v>
       </c>
@@ -47861,8 +47872,8 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="7" spans="2:32" ht="60.75">
-      <c r="B7" s="462"/>
+    <row r="7" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="464"/>
       <c r="C7" s="296" t="s">
         <v>86</v>
       </c>
@@ -47912,8 +47923,8 @@
       <c r="AA7" s="231"/>
       <c r="AD7" s="276"/>
     </row>
-    <row r="8" spans="2:32" ht="60.75">
-      <c r="B8" s="462"/>
+    <row r="8" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="464"/>
       <c r="C8" s="296" t="s">
         <v>86</v>
       </c>
@@ -47970,8 +47981,8 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="9" spans="2:32" ht="63">
-      <c r="B9" s="462"/>
+    <row r="9" spans="2:32" ht="63" x14ac:dyDescent="0.25">
+      <c r="B9" s="464"/>
       <c r="C9" s="296" t="s">
         <v>86</v>
       </c>
@@ -48018,8 +48029,8 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="10" spans="2:32" ht="45" customHeight="1">
-      <c r="B10" s="462"/>
+    <row r="10" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="464"/>
       <c r="C10" s="296" t="s">
         <v>86</v>
       </c>
@@ -48078,8 +48089,8 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="11" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B11" s="470"/>
+    <row r="11" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="472"/>
       <c r="C11" s="296" t="s">
         <v>86</v>
       </c>
@@ -48138,7 +48149,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="12" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1">
+    <row r="12" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="292"/>
       <c r="C12" s="292"/>
       <c r="D12" s="292"/>
@@ -48172,8 +48183,8 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="13" spans="2:32" ht="60.75">
-      <c r="B13" s="459" t="s">
+    <row r="13" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="461" t="s">
         <v>213</v>
       </c>
       <c r="C13" s="285" t="s">
@@ -48230,8 +48241,8 @@
       </c>
       <c r="AF13" s="276"/>
     </row>
-    <row r="14" spans="2:32" ht="60.75">
-      <c r="B14" s="460"/>
+    <row r="14" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="462"/>
       <c r="C14" s="285" t="s">
         <v>86</v>
       </c>
@@ -48285,8 +48296,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="2:32" ht="45" customHeight="1">
-      <c r="B15" s="460"/>
+    <row r="15" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="462"/>
       <c r="C15" s="285" t="s">
         <v>86</v>
       </c>
@@ -48342,8 +48353,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B16" s="497"/>
+    <row r="16" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="493"/>
       <c r="C16" s="285" t="s">
         <v>86</v>
       </c>
@@ -48399,7 +48410,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1">
+    <row r="17" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="292"/>
       <c r="C17" s="292"/>
       <c r="D17" s="292"/>
@@ -48430,8 +48441,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:32" ht="60.75">
-      <c r="B18" s="461" t="s">
+    <row r="18" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="463" t="s">
         <v>214</v>
       </c>
       <c r="C18" s="296" t="s">
@@ -48487,8 +48498,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:32" ht="60.75">
-      <c r="B19" s="462"/>
+    <row r="19" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="464"/>
       <c r="C19" s="296" t="s">
         <v>86</v>
       </c>
@@ -48542,8 +48553,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:32" ht="45" customHeight="1">
-      <c r="B20" s="462"/>
+    <row r="20" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="464"/>
       <c r="C20" s="296" t="s">
         <v>86</v>
       </c>
@@ -48599,8 +48610,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B21" s="470"/>
+    <row r="21" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="472"/>
       <c r="C21" s="296" t="s">
         <v>86</v>
       </c>
@@ -48656,7 +48667,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1">
+    <row r="22" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="292"/>
       <c r="C22" s="292"/>
       <c r="D22" s="292"/>
@@ -48685,8 +48696,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:32" ht="60.75">
-      <c r="B23" s="459" t="s">
+    <row r="23" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="461" t="s">
         <v>215</v>
       </c>
       <c r="C23" s="285" t="s">
@@ -48743,8 +48754,8 @@
       </c>
       <c r="AF23" s="276"/>
     </row>
-    <row r="24" spans="2:32" ht="60.75">
-      <c r="B24" s="460"/>
+    <row r="24" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="462"/>
       <c r="C24" s="285" t="s">
         <v>86</v>
       </c>
@@ -48798,8 +48809,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="2:32" ht="45" customHeight="1">
-      <c r="B25" s="460"/>
+    <row r="25" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="462"/>
       <c r="C25" s="285" t="s">
         <v>86</v>
       </c>
@@ -48855,8 +48866,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B26" s="497"/>
+    <row r="26" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="493"/>
       <c r="C26" s="285" t="s">
         <v>86</v>
       </c>
@@ -48912,7 +48923,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:32" s="274" customFormat="1" ht="7.5" customHeight="1" thickBot="1">
+    <row r="27" spans="2:32" s="274" customFormat="1" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="292"/>
       <c r="C27" s="292"/>
       <c r="D27" s="292"/>
@@ -48941,8 +48952,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:32" ht="60.75">
-      <c r="B28" s="461" t="s">
+    <row r="28" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="463" t="s">
         <v>216</v>
       </c>
       <c r="C28" s="296" t="s">
@@ -48998,8 +49009,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:32" ht="60.75">
-      <c r="B29" s="462"/>
+    <row r="29" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="464"/>
       <c r="C29" s="296" t="s">
         <v>86</v>
       </c>
@@ -49053,8 +49064,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:32" ht="45" customHeight="1">
-      <c r="B30" s="462"/>
+    <row r="30" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="464"/>
       <c r="C30" s="296" t="s">
         <v>86</v>
       </c>
@@ -49110,8 +49121,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B31" s="470"/>
+    <row r="31" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="472"/>
       <c r="C31" s="296" t="s">
         <v>86</v>
       </c>
@@ -49167,7 +49178,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="2:32" s="274" customFormat="1" ht="9" customHeight="1" thickBot="1">
+    <row r="32" spans="2:32" s="274" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="292"/>
       <c r="C32" s="292"/>
       <c r="D32" s="292"/>
@@ -49196,8 +49207,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:32" ht="60.75">
-      <c r="B33" s="459" t="s">
+    <row r="33" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="461" t="s">
         <v>217</v>
       </c>
       <c r="C33" s="285" t="s">
@@ -49254,8 +49265,8 @@
       </c>
       <c r="AF33" s="276"/>
     </row>
-    <row r="34" spans="2:32" ht="60.75">
-      <c r="B34" s="460"/>
+    <row r="34" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="462"/>
       <c r="C34" s="285" t="s">
         <v>86</v>
       </c>
@@ -49309,8 +49320,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:32" ht="45" customHeight="1">
-      <c r="B35" s="460"/>
+    <row r="35" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="462"/>
       <c r="C35" s="285" t="s">
         <v>86</v>
       </c>
@@ -49366,8 +49377,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B36" s="497"/>
+    <row r="36" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="493"/>
       <c r="C36" s="285" t="s">
         <v>86</v>
       </c>
@@ -49423,7 +49434,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1">
+    <row r="37" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="292"/>
       <c r="C37" s="292"/>
       <c r="D37" s="292"/>
@@ -49452,8 +49463,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:32" ht="60.75">
-      <c r="B38" s="461" t="s">
+    <row r="38" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="463" t="s">
         <v>218</v>
       </c>
       <c r="C38" s="296" t="s">
@@ -49509,8 +49520,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:32" ht="60.75">
-      <c r="B39" s="462"/>
+    <row r="39" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="464"/>
       <c r="C39" s="296" t="s">
         <v>86</v>
       </c>
@@ -49564,8 +49575,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:32" ht="45" customHeight="1">
-      <c r="B40" s="462"/>
+    <row r="40" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="464"/>
       <c r="C40" s="296" t="s">
         <v>86</v>
       </c>
@@ -49621,8 +49632,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B41" s="470"/>
+    <row r="41" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="472"/>
       <c r="C41" s="296" t="s">
         <v>86</v>
       </c>
@@ -49678,7 +49689,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1">
+    <row r="42" spans="2:32" s="274" customFormat="1" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="292"/>
       <c r="C42" s="292"/>
       <c r="D42" s="292"/>
@@ -49707,8 +49718,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="2:32" ht="60.75">
-      <c r="B43" s="459" t="s">
+    <row r="43" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="461" t="s">
         <v>219</v>
       </c>
       <c r="C43" s="285" t="s">
@@ -49765,8 +49776,8 @@
       </c>
       <c r="AF43" s="276"/>
     </row>
-    <row r="44" spans="2:32" ht="60.75">
-      <c r="B44" s="460"/>
+    <row r="44" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="462"/>
       <c r="C44" s="285" t="s">
         <v>86</v>
       </c>
@@ -49820,8 +49831,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="2:32" ht="45" customHeight="1">
-      <c r="B45" s="460"/>
+    <row r="45" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="462"/>
       <c r="C45" s="285" t="s">
         <v>86</v>
       </c>
@@ -49877,8 +49888,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B46" s="497"/>
+    <row r="46" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="493"/>
       <c r="C46" s="285" t="s">
         <v>86</v>
       </c>
@@ -49934,7 +49945,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="2:32" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1">
+    <row r="47" spans="2:32" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="292"/>
       <c r="C47" s="292"/>
       <c r="D47" s="292"/>
@@ -49963,8 +49974,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="2:32" ht="60.75">
-      <c r="B48" s="461" t="s">
+    <row r="48" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="463" t="s">
         <v>220</v>
       </c>
       <c r="C48" s="296" t="s">
@@ -50020,8 +50031,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="2:32" ht="45" customHeight="1">
-      <c r="B49" s="462"/>
+    <row r="49" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="464"/>
       <c r="C49" s="296" t="s">
         <v>86</v>
       </c>
@@ -50075,8 +50086,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="2:32" ht="45" customHeight="1">
-      <c r="B50" s="462"/>
+    <row r="50" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="464"/>
       <c r="C50" s="296" t="s">
         <v>86</v>
       </c>
@@ -50132,8 +50143,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="2:32" ht="45" customHeight="1" thickBot="1">
-      <c r="B51" s="470"/>
+    <row r="51" spans="2:32" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="472"/>
       <c r="C51" s="296" t="s">
         <v>86</v>
       </c>
@@ -50189,7 +50200,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="2:32" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="52" spans="2:32" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="292"/>
       <c r="C52" s="292"/>
       <c r="D52" s="292" t="s">
@@ -50222,8 +50233,8 @@
       </c>
       <c r="AE52" s="230"/>
     </row>
-    <row r="53" spans="2:32" ht="60.75">
-      <c r="B53" s="459" t="s">
+    <row r="53" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="461" t="s">
         <v>221</v>
       </c>
       <c r="C53" s="285" t="s">
@@ -50280,8 +50291,8 @@
       </c>
       <c r="AF53" s="276"/>
     </row>
-    <row r="54" spans="2:32" ht="60.75">
-      <c r="B54" s="460"/>
+    <row r="54" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="462"/>
       <c r="C54" s="285" t="s">
         <v>86</v>
       </c>
@@ -50335,8 +50346,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="2:32" ht="60.75">
-      <c r="B55" s="460"/>
+    <row r="55" spans="2:32" ht="60.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="462"/>
       <c r="C55" s="285" t="s">
         <v>86</v>
       </c>
@@ -50392,8 +50403,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="2:32" ht="61.5" thickBot="1">
-      <c r="B56" s="497"/>
+    <row r="56" spans="2:32" ht="61.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="493"/>
       <c r="C56" s="285" t="s">
         <v>86</v>
       </c>
@@ -50449,7 +50460,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="2:32" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1">
+    <row r="57" spans="2:32" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="292"/>
       <c r="C57" s="292"/>
       <c r="D57" s="292"/>
@@ -50477,8 +50488,8 @@
       <c r="AA57" s="126"/>
       <c r="AE57" s="230"/>
     </row>
-    <row r="58" spans="2:32" ht="45" customHeight="1">
-      <c r="B58" s="461" t="s">
+    <row r="58" spans="2:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="463" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="296" t="s">
@@ -50534,8 +50545,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="2:32" ht="57.75">
-      <c r="B59" s="462"/>
+    <row r="59" spans="2:32" ht="57.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="464"/>
       <c r="C59" s="296" t="s">
         <v>125</v>
       </c>
@@ -50589,8 +50600,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="2:32" ht="58.5" thickBot="1">
-      <c r="B60" s="470"/>
+    <row r="60" spans="2:32" ht="58.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="472"/>
       <c r="C60" s="296" t="s">
         <v>125</v>
       </c>
@@ -50644,7 +50655,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="2:32" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="61" spans="2:32" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="292"/>
       <c r="C61" s="292"/>
       <c r="D61" s="292"/>
@@ -50671,7 +50682,7 @@
       <c r="AA61" s="275"/>
       <c r="AB61" s="275"/>
     </row>
-    <row r="62" spans="2:32" s="274" customFormat="1" ht="171.75" thickBot="1">
+    <row r="62" spans="2:32" s="274" customFormat="1" ht="171.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="303" t="s">
         <v>130</v>
       </c>
@@ -50728,7 +50739,7 @@
       </c>
       <c r="AB62" s="275"/>
     </row>
-    <row r="63" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1">
+    <row r="63" spans="2:32" s="274" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="270"/>
       <c r="C63" s="270"/>
       <c r="D63" s="270"/>
@@ -50755,8 +50766,8 @@
       <c r="AA63" s="23"/>
       <c r="AB63" s="231"/>
     </row>
-    <row r="64" spans="2:32" ht="28.9" customHeight="1">
-      <c r="B64" s="471" t="s">
+    <row r="64" spans="2:32" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="473" t="s">
         <v>135</v>
       </c>
       <c r="C64" s="306" t="s">
@@ -50810,8 +50821,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:29" ht="28.9" customHeight="1">
-      <c r="B65" s="472"/>
+    <row r="65" spans="2:29" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="474"/>
       <c r="C65" s="307" t="s">
         <v>135</v>
       </c>
@@ -50864,8 +50875,8 @@
       </c>
       <c r="AB65" s="274"/>
     </row>
-    <row r="66" spans="2:29" ht="28.9" customHeight="1">
-      <c r="B66" s="472"/>
+    <row r="66" spans="2:29" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="474"/>
       <c r="C66" s="307" t="s">
         <v>135</v>
       </c>
@@ -50917,8 +50928,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="2:29" ht="28.9" customHeight="1">
-      <c r="B67" s="472"/>
+    <row r="67" spans="2:29" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="474"/>
       <c r="C67" s="307" t="s">
         <v>135</v>
       </c>
@@ -50970,8 +50981,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="2:29" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B68" s="473"/>
+    <row r="68" spans="2:29" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="475"/>
       <c r="C68" s="308" t="s">
         <v>135</v>
       </c>
@@ -51023,7 +51034,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="2:29" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="69" spans="2:29" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="292"/>
       <c r="C69" s="292"/>
       <c r="D69" s="292"/>
@@ -51048,8 +51059,8 @@
       <c r="W69" s="292"/>
       <c r="X69" s="295"/>
     </row>
-    <row r="70" spans="2:29" ht="49.5">
-      <c r="B70" s="463" t="s">
+    <row r="70" spans="2:29" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B70" s="465" t="s">
         <v>136</v>
       </c>
       <c r="C70" s="244" t="s">
@@ -51103,8 +51114,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="2:29" ht="50.25" thickBot="1">
-      <c r="B71" s="464"/>
+    <row r="71" spans="2:29" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="466"/>
       <c r="C71" s="309" t="s">
         <v>136</v>
       </c>
@@ -51158,7 +51169,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:29" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1">
+    <row r="72" spans="2:29" s="274" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="292"/>
       <c r="C72" s="292"/>
       <c r="D72" s="292"/>
@@ -51186,8 +51197,8 @@
       <c r="AB72" s="231"/>
       <c r="AC72" s="231"/>
     </row>
-    <row r="73" spans="2:29" ht="141.75">
-      <c r="B73" s="465" t="s">
+    <row r="73" spans="2:29" ht="141.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="467" t="s">
         <v>139</v>
       </c>
       <c r="C73" s="310" t="s">
@@ -51243,8 +51254,8 @@
       <c r="AB73" s="275"/>
       <c r="AC73" s="275"/>
     </row>
-    <row r="74" spans="2:29" ht="47.25" thickBot="1">
-      <c r="B74" s="466"/>
+    <row r="74" spans="2:29" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="468"/>
       <c r="C74" s="313" t="s">
         <v>139</v>
       </c>
@@ -51298,7 +51309,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="75" spans="2:29" s="274" customFormat="1" ht="7.5" customHeight="1" thickBot="1">
+    <row r="75" spans="2:29" s="274" customFormat="1" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="292"/>
       <c r="C75" s="292"/>
       <c r="D75" s="292"/>
@@ -51326,11 +51337,11 @@
       <c r="AB75" s="231"/>
       <c r="AC75" s="231"/>
     </row>
-    <row r="76" spans="2:29" ht="23.25" customHeight="1" thickBot="1">
-      <c r="B76" s="456" t="s">
+    <row r="76" spans="2:29" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="458" t="s">
         <v>143</v>
       </c>
-      <c r="C76" s="489" t="s">
+      <c r="C76" s="416" t="s">
         <v>91</v>
       </c>
       <c r="D76" s="69" t="s">
@@ -51379,9 +51390,11 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="2:29" ht="28.9" customHeight="1">
-      <c r="B77" s="457"/>
-      <c r="C77" s="490"/>
+    <row r="77" spans="2:29" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="459"/>
+      <c r="C77" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D77" s="93" t="s">
         <v>227</v>
       </c>
@@ -51432,9 +51445,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="2:29" ht="28.9" customHeight="1">
-      <c r="B78" s="457"/>
-      <c r="C78" s="490"/>
+    <row r="78" spans="2:29" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="459"/>
+      <c r="C78" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D78" s="93" t="s">
         <v>7</v>
       </c>
@@ -51483,9 +51498,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="2:29" ht="108" customHeight="1">
-      <c r="B79" s="457"/>
-      <c r="C79" s="490"/>
+    <row r="79" spans="2:29" ht="108" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="459"/>
+      <c r="C79" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D79" s="93" t="s">
         <v>228</v>
       </c>
@@ -51536,9 +51553,11 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="2:29" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B80" s="458"/>
-      <c r="C80" s="491"/>
+    <row r="80" spans="2:29" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="460"/>
+      <c r="C80" s="416" t="s">
+        <v>91</v>
+      </c>
       <c r="D80" s="95" t="s">
         <v>205</v>
       </c>
@@ -51589,7 +51608,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="2:29" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="81" spans="2:29" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="292"/>
       <c r="C81" s="292"/>
       <c r="D81" s="292"/>
@@ -51617,8 +51636,8 @@
       <c r="AB81" s="231"/>
       <c r="AC81" s="231"/>
     </row>
-    <row r="82" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B82" s="465" t="s">
+    <row r="82" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="467" t="s">
         <v>155</v>
       </c>
       <c r="C82" s="310" t="s">
@@ -51674,8 +51693,8 @@
       <c r="AB82" s="275"/>
       <c r="AC82" s="275"/>
     </row>
-    <row r="83" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B83" s="496"/>
+    <row r="83" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="492"/>
       <c r="C83" s="325" t="s">
         <v>156</v>
       </c>
@@ -51727,8 +51746,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="84" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B84" s="496"/>
+    <row r="84" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="492"/>
       <c r="C84" s="325" t="s">
         <v>156</v>
       </c>
@@ -51782,8 +51801,8 @@
       <c r="AB84" s="275"/>
       <c r="AC84" s="275"/>
     </row>
-    <row r="85" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B85" s="496"/>
+    <row r="85" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="492"/>
       <c r="C85" s="325" t="s">
         <v>156</v>
       </c>
@@ -51835,8 +51854,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="86" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B86" s="496"/>
+    <row r="86" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="492"/>
       <c r="C86" s="325" t="s">
         <v>156</v>
       </c>
@@ -51888,8 +51907,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="2:29" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B87" s="466"/>
+    <row r="87" spans="2:29" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="468"/>
       <c r="C87" s="313" t="s">
         <v>156</v>
       </c>
@@ -51941,26 +51960,25 @@
         <v>156</v>
       </c>
     </row>
-    <row r="88" spans="2:29" ht="14.25" customHeight="1"/>
+    <row r="88" spans="2:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="B82:B87"/>
     <mergeCell ref="B58:B60"/>
     <mergeCell ref="B64:B68"/>
     <mergeCell ref="B70:B71"/>
     <mergeCell ref="B73:B74"/>
     <mergeCell ref="B76:B80"/>
-    <mergeCell ref="C76:C80"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="B38:B41"/>
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B48:B51"/>
+    <mergeCell ref="B53:B56"/>
     <mergeCell ref="B5:B11"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B23:B26"/>
     <mergeCell ref="B28:B31"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="B38:B41"/>
-    <mergeCell ref="B43:B46"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="B53:B56"/>
   </mergeCells>
   <conditionalFormatting sqref="M1:M1048576">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
@@ -51999,7 +52017,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B1:AE87"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.75" style="230" customWidth="1"/>
     <col min="2" max="2" width="16" style="230" customWidth="1"/>
@@ -52027,7 +52045,7 @@
     <col min="30" max="16384" width="9" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:31" ht="5.45" customHeight="1">
+    <row r="1" spans="2:31" ht="5.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F1" s="257"/>
       <c r="G1" s="257"/>
       <c r="H1" s="257"/>
@@ -52040,7 +52058,7 @@
       <c r="M1" s="258"/>
       <c r="O1" s="346"/>
     </row>
-    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1">
+    <row r="2" spans="2:31" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="261"/>
       <c r="C2" s="261" t="s">
         <v>96</v>
@@ -52107,7 +52125,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="3" spans="2:31" ht="45" hidden="1" customHeight="1">
+    <row r="3" spans="2:31" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="262"/>
       <c r="C3" s="262"/>
       <c r="D3" s="263" t="s">
@@ -52155,7 +52173,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="4" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="292"/>
       <c r="C4" s="292"/>
       <c r="D4" s="292"/>
@@ -52183,8 +52201,8 @@
       <c r="AA4" s="275"/>
       <c r="AB4" s="275"/>
     </row>
-    <row r="5" spans="2:31" ht="45" customHeight="1">
-      <c r="B5" s="498" t="s">
+    <row r="5" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="494" t="s">
         <v>104</v>
       </c>
       <c r="C5" s="332" t="s">
@@ -52245,8 +52263,8 @@
         <v>46166</v>
       </c>
     </row>
-    <row r="6" spans="2:31" ht="45" customHeight="1">
-      <c r="B6" s="462"/>
+    <row r="6" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="464"/>
       <c r="C6" s="296" t="s">
         <v>86</v>
       </c>
@@ -52297,8 +52315,8 @@
       <c r="Z6" s="231"/>
       <c r="AC6" s="276"/>
     </row>
-    <row r="7" spans="2:31" ht="45" customHeight="1">
-      <c r="B7" s="462"/>
+    <row r="7" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="464"/>
       <c r="C7" s="296" t="s">
         <v>86</v>
       </c>
@@ -52349,8 +52367,8 @@
       <c r="Z7" s="231"/>
       <c r="AC7" s="276"/>
     </row>
-    <row r="8" spans="2:31" ht="45" customHeight="1">
-      <c r="B8" s="462"/>
+    <row r="8" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="464"/>
       <c r="C8" s="296" t="s">
         <v>86</v>
       </c>
@@ -52406,8 +52424,8 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="9" spans="2:31" ht="45" customHeight="1">
-      <c r="B9" s="462"/>
+    <row r="9" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="464"/>
       <c r="C9" s="296" t="s">
         <v>86</v>
       </c>
@@ -52453,8 +52471,8 @@
         <v>46168</v>
       </c>
     </row>
-    <row r="10" spans="2:31" ht="45" customHeight="1">
-      <c r="B10" s="462"/>
+    <row r="10" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="464"/>
       <c r="C10" s="296" t="s">
         <v>86</v>
       </c>
@@ -52512,8 +52530,8 @@
         <v>46169</v>
       </c>
     </row>
-    <row r="11" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B11" s="462"/>
+    <row r="11" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="464"/>
       <c r="C11" s="296" t="s">
         <v>86</v>
       </c>
@@ -52571,7 +52589,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="12" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="12" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="292"/>
       <c r="C12" s="292"/>
       <c r="D12" s="292" t="s">
@@ -52604,8 +52622,8 @@
         <v>46288</v>
       </c>
     </row>
-    <row r="13" spans="2:31" ht="45" customHeight="1">
-      <c r="B13" s="459" t="s">
+    <row r="13" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="461" t="s">
         <v>168</v>
       </c>
       <c r="C13" s="285" t="s">
@@ -52664,8 +52682,8 @@
       </c>
       <c r="AE13" s="276"/>
     </row>
-    <row r="14" spans="2:31" ht="45" customHeight="1">
-      <c r="B14" s="460"/>
+    <row r="14" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="462"/>
       <c r="C14" s="285" t="s">
         <v>86</v>
       </c>
@@ -52718,8 +52736,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="2:31" ht="45" customHeight="1">
-      <c r="B15" s="460"/>
+    <row r="15" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="462"/>
       <c r="C15" s="285" t="s">
         <v>86</v>
       </c>
@@ -52774,8 +52792,8 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B16" s="460"/>
+    <row r="16" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="462"/>
       <c r="C16" s="285" t="s">
         <v>86</v>
       </c>
@@ -52830,7 +52848,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="17" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="292"/>
       <c r="C17" s="292"/>
       <c r="D17" s="292" t="s">
@@ -52860,8 +52878,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="2:31" ht="45" customHeight="1">
-      <c r="B18" s="461" t="s">
+    <row r="18" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="463" t="s">
         <v>233</v>
       </c>
       <c r="C18" s="296" t="s">
@@ -52916,8 +52934,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="19" spans="2:31" ht="45" customHeight="1">
-      <c r="B19" s="462"/>
+    <row r="19" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="464"/>
       <c r="C19" s="296" t="s">
         <v>86</v>
       </c>
@@ -52970,8 +52988,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="2:31" ht="45" customHeight="1">
-      <c r="B20" s="462"/>
+    <row r="20" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="464"/>
       <c r="C20" s="296" t="s">
         <v>86</v>
       </c>
@@ -53026,8 +53044,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="21" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B21" s="462"/>
+    <row r="21" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="464"/>
       <c r="C21" s="296" t="s">
         <v>86</v>
       </c>
@@ -53082,7 +53100,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="22" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="292"/>
       <c r="C22" s="292"/>
       <c r="D22" s="292" t="s">
@@ -53112,8 +53130,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="2:31" ht="45" customHeight="1">
-      <c r="B23" s="459" t="s">
+    <row r="23" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="461" t="s">
         <v>234</v>
       </c>
       <c r="C23" s="285" t="s">
@@ -53169,8 +53187,8 @@
       </c>
       <c r="AE23" s="276"/>
     </row>
-    <row r="24" spans="2:31" ht="45" customHeight="1">
-      <c r="B24" s="460"/>
+    <row r="24" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="462"/>
       <c r="C24" s="285" t="s">
         <v>86</v>
       </c>
@@ -53223,8 +53241,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="2:31" ht="45" customHeight="1">
-      <c r="B25" s="460"/>
+    <row r="25" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="462"/>
       <c r="C25" s="285" t="s">
         <v>86</v>
       </c>
@@ -53279,8 +53297,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B26" s="460"/>
+    <row r="26" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="462"/>
       <c r="C26" s="285" t="s">
         <v>86</v>
       </c>
@@ -53335,7 +53353,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="27" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="292"/>
       <c r="C27" s="292"/>
       <c r="D27" s="292" t="s">
@@ -53365,8 +53383,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:31" ht="45" customHeight="1">
-      <c r="B28" s="461" t="s">
+    <row r="28" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="463" t="s">
         <v>235</v>
       </c>
       <c r="C28" s="296" t="s">
@@ -53421,8 +53439,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="2:31" ht="45" customHeight="1">
-      <c r="B29" s="462"/>
+    <row r="29" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="464"/>
       <c r="C29" s="296" t="s">
         <v>86</v>
       </c>
@@ -53475,8 +53493,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="2:31" ht="45" customHeight="1">
-      <c r="B30" s="462"/>
+    <row r="30" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="464"/>
       <c r="C30" s="296" t="s">
         <v>86</v>
       </c>
@@ -53531,8 +53549,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B31" s="462"/>
+    <row r="31" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="464"/>
       <c r="C31" s="296" t="s">
         <v>86</v>
       </c>
@@ -53587,7 +53605,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="32" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="292"/>
       <c r="C32" s="292"/>
       <c r="D32" s="292" t="s">
@@ -53617,8 +53635,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:31" ht="45" customHeight="1">
-      <c r="B33" s="459" t="s">
+    <row r="33" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="461" t="s">
         <v>236</v>
       </c>
       <c r="C33" s="285" t="s">
@@ -53674,8 +53692,8 @@
       </c>
       <c r="AE33" s="276"/>
     </row>
-    <row r="34" spans="2:31" ht="45" customHeight="1">
-      <c r="B34" s="460"/>
+    <row r="34" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="462"/>
       <c r="C34" s="285" t="s">
         <v>86</v>
       </c>
@@ -53728,8 +53746,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:31" ht="45" customHeight="1">
-      <c r="B35" s="460"/>
+    <row r="35" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="462"/>
       <c r="C35" s="285" t="s">
         <v>86</v>
       </c>
@@ -53784,8 +53802,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="36" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B36" s="460"/>
+    <row r="36" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="462"/>
       <c r="C36" s="285" t="s">
         <v>86</v>
       </c>
@@ -53840,7 +53858,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="37" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="292"/>
       <c r="C37" s="292"/>
       <c r="D37" s="292" t="s">
@@ -53870,8 +53888,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="2:31" ht="45" customHeight="1">
-      <c r="B38" s="461" t="s">
+    <row r="38" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="463" t="s">
         <v>123</v>
       </c>
       <c r="C38" s="296" t="s">
@@ -53926,8 +53944,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="2:31" ht="45" customHeight="1">
-      <c r="B39" s="462"/>
+    <row r="39" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="464"/>
       <c r="C39" s="296" t="s">
         <v>86</v>
       </c>
@@ -53980,8 +53998,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" spans="2:31" ht="45" customHeight="1">
-      <c r="B40" s="462"/>
+    <row r="40" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="464"/>
       <c r="C40" s="296" t="s">
         <v>86</v>
       </c>
@@ -54036,8 +54054,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B41" s="462"/>
+    <row r="41" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="464"/>
       <c r="C41" s="296" t="s">
         <v>86</v>
       </c>
@@ -54092,7 +54110,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="42" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="292"/>
       <c r="C42" s="292"/>
       <c r="D42" s="292" t="s">
@@ -54122,8 +54140,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="2:31" ht="45" customHeight="1">
-      <c r="B43" s="459" t="s">
+    <row r="43" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="461" t="s">
         <v>124</v>
       </c>
       <c r="C43" s="285" t="s">
@@ -54179,8 +54197,8 @@
       </c>
       <c r="AE43" s="276"/>
     </row>
-    <row r="44" spans="2:31" ht="45" customHeight="1">
-      <c r="B44" s="460"/>
+    <row r="44" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="462"/>
       <c r="C44" s="285" t="s">
         <v>86</v>
       </c>
@@ -54233,8 +54251,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="2:31" ht="45" customHeight="1">
-      <c r="B45" s="460"/>
+    <row r="45" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="462"/>
       <c r="C45" s="285" t="s">
         <v>86</v>
       </c>
@@ -54289,8 +54307,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B46" s="460"/>
+    <row r="46" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="462"/>
       <c r="C46" s="285" t="s">
         <v>86</v>
       </c>
@@ -54345,7 +54363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="47" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="292"/>
       <c r="C47" s="292"/>
       <c r="D47" s="292" t="s">
@@ -54375,8 +54393,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="2:31" ht="45" customHeight="1">
-      <c r="B48" s="461" t="s">
+    <row r="48" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="463" t="s">
         <v>237</v>
       </c>
       <c r="C48" s="296" t="s">
@@ -54431,8 +54449,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="49" spans="2:31" ht="45" customHeight="1">
-      <c r="B49" s="462"/>
+    <row r="49" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="464"/>
       <c r="C49" s="296" t="s">
         <v>86</v>
       </c>
@@ -54485,8 +54503,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="2:31" ht="45" customHeight="1">
-      <c r="B50" s="462"/>
+    <row r="50" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="464"/>
       <c r="C50" s="296" t="s">
         <v>86</v>
       </c>
@@ -54541,8 +54559,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B51" s="462"/>
+    <row r="51" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="464"/>
       <c r="C51" s="296" t="s">
         <v>86</v>
       </c>
@@ -54597,7 +54615,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="52" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="292"/>
       <c r="C52" s="292"/>
       <c r="D52" s="292" t="s">
@@ -54631,8 +54649,8 @@
       </c>
       <c r="AD52" s="230"/>
     </row>
-    <row r="53" spans="2:31" ht="45" customHeight="1">
-      <c r="B53" s="459" t="s">
+    <row r="53" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="461" t="s">
         <v>238</v>
       </c>
       <c r="C53" s="285" t="s">
@@ -54688,8 +54706,8 @@
       </c>
       <c r="AE53" s="276"/>
     </row>
-    <row r="54" spans="2:31" ht="45" customHeight="1">
-      <c r="B54" s="460"/>
+    <row r="54" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="462"/>
       <c r="C54" s="285" t="s">
         <v>86</v>
       </c>
@@ -54742,8 +54760,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="2:31" ht="45" customHeight="1">
-      <c r="B55" s="460"/>
+    <row r="55" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="462"/>
       <c r="C55" s="285" t="s">
         <v>86</v>
       </c>
@@ -54798,8 +54816,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="2:31" ht="45" customHeight="1" thickBot="1">
-      <c r="B56" s="460"/>
+    <row r="56" spans="2:31" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B56" s="462"/>
       <c r="C56" s="285" t="s">
         <v>86</v>
       </c>
@@ -54854,7 +54872,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="57" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="292"/>
       <c r="C57" s="292"/>
       <c r="D57" s="292"/>
@@ -54883,8 +54901,8 @@
       <c r="Z57" s="126"/>
       <c r="AD57" s="230"/>
     </row>
-    <row r="58" spans="2:31" ht="45" customHeight="1">
-      <c r="B58" s="461" t="s">
+    <row r="58" spans="2:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="463" t="s">
         <v>125</v>
       </c>
       <c r="C58" s="296" t="s">
@@ -54939,8 +54957,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="2:31" ht="60">
-      <c r="B59" s="462"/>
+    <row r="59" spans="2:31" ht="60" x14ac:dyDescent="0.25">
+      <c r="B59" s="464"/>
       <c r="C59" s="296" t="s">
         <v>125</v>
       </c>
@@ -54993,8 +55011,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="2:31" ht="60.75" thickBot="1">
-      <c r="B60" s="470"/>
+    <row r="60" spans="2:31" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="472"/>
       <c r="C60" s="296" t="s">
         <v>125</v>
       </c>
@@ -55047,7 +55065,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="61" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="61" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="292"/>
       <c r="C61" s="292"/>
       <c r="D61" s="292"/>
@@ -55075,7 +55093,7 @@
       <c r="Z61" s="275"/>
       <c r="AA61" s="275"/>
     </row>
-    <row r="62" spans="2:31" s="274" customFormat="1" ht="85.5" customHeight="1" thickBot="1">
+    <row r="62" spans="2:31" s="274" customFormat="1" ht="85.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B62" s="303" t="s">
         <v>130</v>
       </c>
@@ -55131,7 +55149,7 @@
       </c>
       <c r="AA62" s="275"/>
     </row>
-    <row r="63" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="63" spans="2:31" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="270"/>
       <c r="C63" s="270"/>
       <c r="D63" s="270"/>
@@ -55159,8 +55177,8 @@
       <c r="Z63" s="23"/>
       <c r="AA63" s="231"/>
     </row>
-    <row r="64" spans="2:31" ht="28.9" customHeight="1">
-      <c r="B64" s="471" t="s">
+    <row r="64" spans="2:31" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="473" t="s">
         <v>34</v>
       </c>
       <c r="C64" s="306" t="s">
@@ -55213,8 +55231,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B65" s="472"/>
+    <row r="65" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="474"/>
       <c r="C65" s="307" t="s">
         <v>135</v>
       </c>
@@ -55266,8 +55284,8 @@
       </c>
       <c r="AA65" s="274"/>
     </row>
-    <row r="66" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B66" s="472"/>
+    <row r="66" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="474"/>
       <c r="C66" s="307" t="s">
         <v>135</v>
       </c>
@@ -55318,8 +55336,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="2:28" ht="28.9" customHeight="1">
-      <c r="B67" s="472"/>
+    <row r="67" spans="2:28" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="474"/>
       <c r="C67" s="307" t="s">
         <v>135</v>
       </c>
@@ -55370,8 +55388,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B68" s="473"/>
+    <row r="68" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="475"/>
       <c r="C68" s="308" t="s">
         <v>135</v>
       </c>
@@ -55422,7 +55440,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="69" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="69" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="292"/>
       <c r="C69" s="292"/>
       <c r="D69" s="292"/>
@@ -55448,8 +55466,8 @@
       <c r="V69" s="292"/>
       <c r="W69" s="295"/>
     </row>
-    <row r="70" spans="2:28" ht="34.5" customHeight="1">
-      <c r="B70" s="463" t="s">
+    <row r="70" spans="2:28" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="465" t="s">
         <v>136</v>
       </c>
       <c r="C70" s="244" t="s">
@@ -55500,8 +55518,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="71" spans="2:28" ht="45.75" customHeight="1" thickBot="1">
-      <c r="B71" s="464"/>
+    <row r="71" spans="2:28" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="466"/>
       <c r="C71" s="309" t="s">
         <v>136</v>
       </c>
@@ -55552,7 +55570,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="72" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="72" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B72" s="292"/>
       <c r="C72" s="292"/>
       <c r="D72" s="292"/>
@@ -55581,8 +55599,8 @@
       <c r="AA72" s="231"/>
       <c r="AB72" s="231"/>
     </row>
-    <row r="73" spans="2:28" ht="104.25" customHeight="1">
-      <c r="B73" s="465" t="s">
+    <row r="73" spans="2:28" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="467" t="s">
         <v>139</v>
       </c>
       <c r="C73" s="310" t="s">
@@ -55637,8 +55655,8 @@
       <c r="AA73" s="275"/>
       <c r="AB73" s="275"/>
     </row>
-    <row r="74" spans="2:28" ht="36" customHeight="1" thickBot="1">
-      <c r="B74" s="466"/>
+    <row r="74" spans="2:28" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="468"/>
       <c r="C74" s="313" t="s">
         <v>139</v>
       </c>
@@ -55691,7 +55709,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="75" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="75" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="270"/>
       <c r="C75" s="270"/>
       <c r="D75" s="270"/>
@@ -55720,8 +55738,8 @@
       <c r="AA75" s="231"/>
       <c r="AB75" s="231"/>
     </row>
-    <row r="76" spans="2:28" ht="22.5" customHeight="1" thickBot="1">
-      <c r="B76" s="499" t="s">
+    <row r="76" spans="2:28" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B76" s="495" t="s">
         <v>143</v>
       </c>
       <c r="C76" s="372" t="s">
@@ -55772,8 +55790,8 @@
         <v>144</v>
       </c>
     </row>
-    <row r="77" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B77" s="500"/>
+    <row r="77" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="496"/>
       <c r="C77" s="372" t="s">
         <v>91</v>
       </c>
@@ -55826,8 +55844,8 @@
         <v>147</v>
       </c>
     </row>
-    <row r="78" spans="2:28" ht="63" customHeight="1" thickBot="1">
-      <c r="B78" s="500"/>
+    <row r="78" spans="2:28" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="496"/>
       <c r="C78" s="372" t="s">
         <v>91</v>
       </c>
@@ -55878,8 +55896,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="79" spans="2:28" ht="74.25" customHeight="1" thickBot="1">
-      <c r="B79" s="500"/>
+    <row r="79" spans="2:28" ht="74.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="496"/>
       <c r="C79" s="372" t="s">
         <v>91</v>
       </c>
@@ -55932,8 +55950,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="2:28" ht="28.9" customHeight="1" thickBot="1">
-      <c r="B80" s="501"/>
+    <row r="80" spans="2:28" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="497"/>
       <c r="C80" s="372" t="s">
         <v>91</v>
       </c>
@@ -55986,7 +56004,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="81" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1">
+    <row r="81" spans="2:28" s="274" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="281"/>
       <c r="C81" s="281"/>
       <c r="D81" s="281"/>
@@ -56015,8 +56033,8 @@
       <c r="AA81" s="231"/>
       <c r="AB81" s="231"/>
     </row>
-    <row r="82" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B82" s="467" t="s">
+    <row r="82" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="469" t="s">
         <v>155</v>
       </c>
       <c r="C82" s="317" t="s">
@@ -56071,8 +56089,8 @@
       <c r="AA82" s="275"/>
       <c r="AB82" s="275"/>
     </row>
-    <row r="83" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B83" s="468"/>
+    <row r="83" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="470"/>
       <c r="C83" s="319" t="s">
         <v>156</v>
       </c>
@@ -56123,8 +56141,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="84" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B84" s="468"/>
+    <row r="84" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="470"/>
       <c r="C84" s="319" t="s">
         <v>156</v>
       </c>
@@ -56177,8 +56195,8 @@
       <c r="AA84" s="275"/>
       <c r="AB84" s="275"/>
     </row>
-    <row r="85" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B85" s="468"/>
+    <row r="85" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="470"/>
       <c r="C85" s="319" t="s">
         <v>156</v>
       </c>
@@ -56229,8 +56247,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="86" spans="2:28" ht="30.75" customHeight="1">
-      <c r="B86" s="468"/>
+    <row r="86" spans="2:28" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="470"/>
       <c r="C86" s="319" t="s">
         <v>156</v>
       </c>
@@ -56281,8 +56299,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="2:28" ht="30.75" customHeight="1" thickBot="1">
-      <c r="B87" s="469"/>
+    <row r="87" spans="2:28" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="471"/>
       <c r="C87" s="322" t="s">
         <v>156</v>
       </c>
@@ -56656,13 +56674,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A00D0B-1F3C-4A9C-870E-467A8D18671C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A00D0B-1F3C-4A9C-870E-467A8D18671C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="389f1ef8-9fc7-4250-9466-79c08d8bd832"/>
+    <ds:schemaRef ds:uri="d5b2f26e-b630-44bd-87e5-d5d6c3db68be"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD353690-D15E-4A62-93BF-20497AD3AD6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD353690-D15E-4A62-93BF-20497AD3AD6F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="389f1ef8-9fc7-4250-9466-79c08d8bd832"/>
+    <ds:schemaRef ds:uri="d5b2f26e-b630-44bd-87e5-d5d6c3db68be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70632E2A-9687-457B-BD9D-307E0D3134CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70632E2A-9687-457B-BD9D-307E0D3134CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>